--- a/3.1.1答案/智能音箱数据集.xlsx
+++ b/3.1.1答案/智能音箱数据集.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="24" r:id="rId2"/>
+    <pivotCache cacheId="12" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="1017">
   <si>
     <t>用户ID</t>
   </si>
@@ -3080,13 +3080,19 @@
   </si>
   <si>
     <t>平均值项:响应时间</t>
+  </si>
+  <si>
+    <t>行标签</t>
+  </si>
+  <si>
+    <t>(空白)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3110,7 +3116,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3118,7 +3124,21 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3133,13 +3153,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3170,7 +3188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3183,16 +3201,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="0"/>
@@ -3211,7 +3232,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor indexed="65"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3234,7 +3255,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor indexed="65"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3257,7 +3278,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor indexed="65"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3280,7 +3301,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor indexed="65"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
@@ -3303,76 +3324,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF9C6500"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF9C6500"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor indexed="65"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
@@ -3395,54 +3347,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
+          <fgColor indexed="65"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF9C6500"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3460,9 +3366,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="adm" refreshedDate="46280.430226041666" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="1001">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="adm" refreshedDate="46316.466450694446" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="1001">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D1002" sheet="Sheet1"/>
+    <worksheetSource ref="A1:D1048576" sheet="Sheet1"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="用户ID" numFmtId="0">
@@ -3485,210 +3391,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="响应时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1" maxValue="3" count="202">
-        <n v="1.53"/>
-        <n v="1.97"/>
-        <n v="2.61"/>
-        <n v="2.36"/>
-        <n v="1.69"/>
-        <n v="1.86"/>
-        <n v="2.1800000000000002"/>
-        <n v="1.95"/>
-        <n v="2.2799999999999998"/>
-        <n v="1.1299999999999999"/>
-        <n v="1.65"/>
-        <n v="1.25"/>
-        <n v="1.77"/>
-        <n v="1.82"/>
-        <n v="1.07"/>
-        <n v="1.51"/>
-        <n v="2.91"/>
-        <n v="2.87"/>
-        <n v="1.92"/>
-        <n v="2.69"/>
-        <n v="1.04"/>
-        <n v="1.1399999999999999"/>
-        <n v="2.78"/>
-        <n v="1.42"/>
-        <n v="2.02"/>
-        <n v="2.93"/>
-        <n v="2.4500000000000002"/>
-        <n v="2.5299999999999998"/>
-        <n v="2.67"/>
-        <n v="2.19"/>
-        <n v="1.96"/>
-        <n v="1.32"/>
-        <n v="1.43"/>
-        <n v="1.68"/>
-        <n v="2.1"/>
-        <n v="2.23"/>
-        <n v="2.85"/>
-        <n v="1.58"/>
-        <n v="1.91"/>
-        <n v="1.93"/>
-        <n v="2.34"/>
-        <n v="2.08"/>
-        <n v="1.37"/>
-        <n v="1.52"/>
-        <n v="2.5499999999999998"/>
-        <n v="2.29"/>
-        <n v="1.19"/>
-        <n v="1.24"/>
-        <n v="2.71"/>
-        <n v="2.56"/>
-        <n v="2.52"/>
-        <n v="1.46"/>
-        <n v="2.35"/>
-        <n v="2.5"/>
-        <n v="2.5099999999999998"/>
-        <n v="2.72"/>
-        <n v="2.9"/>
-        <n v="2.41"/>
-        <n v="1.36"/>
-        <n v="1.33"/>
-        <n v="1.71"/>
-        <n v="1.2"/>
-        <n v="2.44"/>
-        <n v="2.98"/>
-        <n v="1.29"/>
-        <n v="1.66"/>
-        <n v="1.54"/>
-        <n v="1.1499999999999999"/>
-        <n v="1.03"/>
-        <n v="1.8"/>
-        <n v="1.1000000000000001"/>
-        <n v="2.39"/>
-        <n v="2.76"/>
-        <n v="1.87"/>
-        <n v="1.02"/>
-        <n v="2.8"/>
-        <n v="2.42"/>
-        <n v="2.63"/>
-        <n v="1.35"/>
-        <n v="1.84"/>
-        <n v="1.31"/>
-        <n v="2.25"/>
-        <n v="1.88"/>
-        <n v="2.48"/>
-        <n v="1.45"/>
-        <n v="1.78"/>
-        <n v="2.68"/>
-        <n v="1.22"/>
-        <n v="2.73"/>
-        <n v="2.57"/>
-        <n v="1.6"/>
-        <n v="2.97"/>
-        <n v="1.56"/>
-        <n v="2.89"/>
-        <n v="2.0299999999999998"/>
-        <n v="1.1200000000000001"/>
-        <n v="2.2599999999999998"/>
-        <n v="1.75"/>
-        <n v="2.33"/>
-        <n v="2.6"/>
-        <n v="1.1599999999999999"/>
-        <n v="1.1100000000000001"/>
-        <n v="1.38"/>
-        <n v="1.89"/>
-        <n v="1.4"/>
-        <n v="1.5"/>
-        <n v="2.16"/>
-        <n v="2.38"/>
-        <n v="2.95"/>
-        <n v="2.82"/>
-        <n v="2.7"/>
-        <n v="1.9"/>
-        <n v="2.66"/>
-        <n v="1.21"/>
-        <n v="2.2200000000000002"/>
-        <n v="1.64"/>
-        <n v="2.2400000000000002"/>
-        <n v="1.99"/>
-        <n v="2.4900000000000002"/>
-        <n v="1.23"/>
-        <n v="2.11"/>
-        <n v="2.77"/>
-        <n v="2.4700000000000002"/>
-        <n v="1"/>
-        <n v="1.85"/>
-        <n v="1.27"/>
-        <n v="2.2999999999999998"/>
-        <n v="1.06"/>
-        <n v="2.13"/>
-        <n v="1.59"/>
-        <n v="1.01"/>
-        <n v="2.86"/>
-        <n v="2.79"/>
-        <n v="2.12"/>
-        <n v="1.7"/>
-        <n v="2.46"/>
-        <n v="3"/>
-        <n v="2.88"/>
-        <n v="2.17"/>
-        <n v="1.08"/>
-        <n v="2.64"/>
-        <n v="1.05"/>
-        <n v="1.81"/>
-        <n v="1.62"/>
-        <n v="1.63"/>
-        <n v="1.41"/>
-        <n v="1.3"/>
-        <n v="2.21"/>
-        <n v="2.54"/>
-        <n v="1.83"/>
-        <n v="2.84"/>
-        <n v="1.18"/>
-        <n v="2.31"/>
-        <n v="1.49"/>
-        <n v="2.81"/>
-        <n v="2.59"/>
-        <n v="1.76"/>
-        <n v="1.61"/>
-        <n v="2.75"/>
-        <n v="1.67"/>
-        <n v="2.04"/>
-        <n v="2.4"/>
-        <n v="1.94"/>
-        <n v="2.15"/>
-        <n v="2.09"/>
-        <n v="2.92"/>
-        <n v="2.27"/>
-        <n v="1.98"/>
-        <n v="1.44"/>
-        <n v="2.0099999999999998"/>
-        <n v="1.57"/>
-        <n v="1.73"/>
-        <n v="1.28"/>
-        <n v="2.14"/>
-        <n v="2"/>
-        <n v="2.99"/>
-        <n v="2.74"/>
-        <n v="1.72"/>
-        <n v="2.0499999999999998"/>
-        <n v="2.37"/>
-        <n v="1.39"/>
-        <n v="2.96"/>
-        <n v="2.83"/>
-        <n v="2.62"/>
-        <n v="2.3199999999999998"/>
-        <n v="1.74"/>
-        <n v="1.0900000000000001"/>
-        <n v="1.79"/>
-        <n v="1.34"/>
-        <n v="2.58"/>
-        <n v="1.26"/>
-        <n v="2.65"/>
-        <n v="2.94"/>
-        <n v="2.2000000000000002"/>
-        <n v="2.4300000000000002"/>
-        <n v="1.47"/>
-        <n v="1.17"/>
-        <n v="1.55"/>
-        <n v="2.06"/>
-        <n v="1.48"/>
-        <n v="2.0699999999999998"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1" maxValue="3"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -3705,6014 +3408,6014 @@
     <n v="47"/>
     <s v="2023-03-26 02:22:30"/>
     <x v="0"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="92"/>
     <s v="2023-04-15 19:44:05"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="1.97"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-02-28 13:45:13"/>
     <x v="2"/>
-    <x v="2"/>
+    <n v="2.61"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-05-03 17:59:11"/>
     <x v="3"/>
-    <x v="3"/>
+    <n v="2.36"/>
   </r>
   <r>
     <n v="48"/>
     <s v="2023-06-12 14:01:51"/>
     <x v="4"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-10-21 10:53:58"/>
     <x v="5"/>
-    <x v="5"/>
+    <n v="1.86"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-08-17 18:20:29"/>
     <x v="6"/>
-    <x v="6"/>
+    <n v="2.1800000000000002"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-02-05 11:04:15"/>
     <x v="4"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-07-03 02:39:49"/>
     <x v="4"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-05-23 08:08:45"/>
     <x v="1"/>
-    <x v="9"/>
+    <n v="1.1299999999999999"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-08-21 17:36:25"/>
     <x v="3"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-02-22 17:29:53"/>
     <x v="4"/>
-    <x v="11"/>
+    <n v="1.25"/>
   </r>
   <r>
     <n v="2"/>
     <s v="2023-08-21 05:29:08"/>
     <x v="1"/>
-    <x v="12"/>
+    <n v="1.77"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-01-05 09:46:26"/>
     <x v="2"/>
-    <x v="13"/>
+    <n v="1.82"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-08-12 10:38:18"/>
     <x v="4"/>
-    <x v="14"/>
+    <n v="1.07"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-03-19 15:12:41"/>
     <x v="7"/>
-    <x v="15"/>
+    <n v="1.51"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-10-30 17:26:21"/>
     <x v="6"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-07-30 09:39:23"/>
     <x v="1"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-05-16 18:54:10"/>
     <x v="4"/>
-    <x v="18"/>
+    <n v="1.92"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-04-27 17:24:55"/>
     <x v="4"/>
-    <x v="19"/>
+    <n v="2.69"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-01-29 10:24:00"/>
     <x v="3"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-05-29 14:00:54"/>
     <x v="5"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-02-23 14:18:46"/>
     <x v="4"/>
-    <x v="11"/>
+    <n v="1.25"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-07-07 23:48:00"/>
     <x v="0"/>
-    <x v="22"/>
+    <n v="2.78"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-03-05 01:25:11"/>
     <x v="1"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-12-06 15:16:21"/>
     <x v="5"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-12-28 20:03:58"/>
     <x v="5"/>
-    <x v="25"/>
+    <n v="2.93"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-08-04 03:51:28"/>
     <x v="3"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-06-07 11:54:20"/>
     <x v="1"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-10-17 02:10:38"/>
     <x v="2"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-05-18 12:47:23"/>
     <x v="2"/>
-    <x v="3"/>
+    <n v="2.36"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-09-16 22:32:06"/>
     <x v="4"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-11-26 14:05:30"/>
     <x v="5"/>
-    <x v="30"/>
+    <n v="1.96"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-03-21 19:10:28"/>
     <x v="5"/>
-    <x v="31"/>
+    <n v="1.32"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-09-02 02:22:30"/>
     <x v="2"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-07-04 19:24:58"/>
     <x v="5"/>
-    <x v="18"/>
+    <n v="1.92"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-07-22 03:45:45"/>
     <x v="2"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-08-02 00:45:14"/>
     <x v="7"/>
-    <x v="34"/>
+    <n v="2.1"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-12-24 03:25:14"/>
     <x v="7"/>
-    <x v="35"/>
+    <n v="2.23"/>
   </r>
   <r>
     <n v="2"/>
     <s v="2023-05-24 05:24:07"/>
     <x v="4"/>
-    <x v="36"/>
+    <n v="2.85"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-08-17 05:12:02"/>
     <x v="7"/>
-    <x v="37"/>
+    <n v="1.58"/>
   </r>
   <r>
     <n v="15"/>
     <s v="2023-11-07 01:08:37"/>
     <x v="5"/>
-    <x v="38"/>
+    <n v="1.91"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-06-25 06:54:31"/>
     <x v="4"/>
-    <x v="39"/>
+    <n v="1.93"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-02-12 21:51:01"/>
     <x v="4"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-10-27 12:24:56"/>
     <x v="2"/>
-    <x v="40"/>
+    <n v="2.34"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-05-27 17:40:20"/>
     <x v="4"/>
-    <x v="41"/>
+    <n v="2.08"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-01-24 06:34:11"/>
     <x v="0"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-08-05 02:02:07"/>
     <x v="4"/>
-    <x v="43"/>
+    <n v="1.52"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-07-02 01:15:06"/>
     <x v="1"/>
-    <x v="44"/>
+    <n v="2.5499999999999998"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-02-28 14:56:49"/>
     <x v="2"/>
-    <x v="45"/>
+    <n v="2.29"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-02-23 01:18:14"/>
     <x v="2"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-08-08 22:41:36"/>
     <x v="4"/>
-    <x v="47"/>
+    <n v="1.24"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-08-14 18:31:18"/>
     <x v="1"/>
-    <x v="48"/>
+    <n v="2.71"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-12-22 03:10:11"/>
     <x v="0"/>
-    <x v="49"/>
+    <n v="2.56"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-03-05 07:58:00"/>
     <x v="2"/>
-    <x v="50"/>
+    <n v="2.52"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-06-30 09:52:12"/>
     <x v="5"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="13"/>
     <s v="2023-06-27 08:19:34"/>
     <x v="5"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-04-24 00:19:32"/>
     <x v="1"/>
-    <x v="52"/>
+    <n v="2.35"/>
   </r>
   <r>
     <n v="73"/>
     <s v="2023-02-12 12:06:03"/>
     <x v="3"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-07-02 06:13:41"/>
     <x v="3"/>
-    <x v="38"/>
+    <n v="1.91"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-08-30 10:48:35"/>
     <x v="5"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-11-19 16:33:31"/>
     <x v="0"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-02-10 14:40:06"/>
     <x v="3"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-12-29 21:30:24"/>
     <x v="6"/>
-    <x v="56"/>
+    <n v="2.9"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-05-04 17:03:02"/>
     <x v="0"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-04-05 00:35:05"/>
     <x v="0"/>
-    <x v="9"/>
+    <n v="1.1299999999999999"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-05-30 01:17:37"/>
     <x v="2"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-08-19 14:46:04"/>
     <x v="4"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-10-02 16:33:08"/>
     <x v="7"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-01-09 10:52:31"/>
     <x v="7"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-11-12 14:26:42"/>
     <x v="2"/>
-    <x v="58"/>
+    <n v="1.36"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-06-11 22:23:33"/>
     <x v="5"/>
-    <x v="59"/>
+    <n v="1.33"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-09-15 18:57:55"/>
     <x v="5"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="93"/>
     <s v="2023-07-24 12:15:55"/>
     <x v="3"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-11-09 09:37:38"/>
     <x v="2"/>
-    <x v="61"/>
+    <n v="1.2"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-01-03 10:47:20"/>
     <x v="4"/>
-    <x v="41"/>
+    <n v="2.08"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-05-01 16:55:52"/>
     <x v="6"/>
-    <x v="62"/>
+    <n v="2.44"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-01-13 10:36:17"/>
     <x v="7"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-12-12 22:25:43"/>
     <x v="3"/>
-    <x v="64"/>
+    <n v="1.29"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-06-02 08:55:24"/>
     <x v="5"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-05-22 20:17:48"/>
     <x v="6"/>
-    <x v="65"/>
+    <n v="1.66"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-02-08 12:37:26"/>
     <x v="0"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-03-15 04:05:49"/>
     <x v="1"/>
-    <x v="48"/>
+    <n v="2.71"/>
   </r>
   <r>
     <n v="13"/>
     <s v="2023-11-13 09:02:05"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="1.97"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-10-29 08:02:28"/>
     <x v="7"/>
-    <x v="58"/>
+    <n v="1.36"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-04-23 08:13:26"/>
     <x v="5"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-11-02 08:01:04"/>
     <x v="5"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-12-19 10:54:20"/>
     <x v="0"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-10-17 10:29:17"/>
     <x v="2"/>
-    <x v="70"/>
+    <n v="1.1000000000000001"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-07-11 23:18:08"/>
     <x v="4"/>
-    <x v="71"/>
+    <n v="2.39"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-03-09 15:48:10"/>
     <x v="6"/>
-    <x v="35"/>
+    <n v="2.23"/>
   </r>
   <r>
     <n v="31"/>
     <s v="2023-06-03 06:05:19"/>
     <x v="1"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-12-23 00:00:14"/>
     <x v="7"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-07-13 09:53:01"/>
     <x v="4"/>
-    <x v="73"/>
+    <n v="1.87"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-06-17 05:07:01"/>
     <x v="1"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-07-28 13:03:08"/>
     <x v="0"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-08-10 16:35:24"/>
     <x v="2"/>
-    <x v="59"/>
+    <n v="1.33"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-06-20 19:14:10"/>
     <x v="3"/>
-    <x v="76"/>
+    <n v="2.42"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-01-18 04:43:17"/>
     <x v="5"/>
-    <x v="77"/>
+    <n v="2.63"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-09-16 21:51:18"/>
     <x v="7"/>
-    <x v="78"/>
+    <n v="1.35"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-10-15 00:03:13"/>
     <x v="6"/>
-    <x v="79"/>
+    <n v="1.84"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-03-09 15:46:51"/>
     <x v="6"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-10-02 08:18:16"/>
     <x v="0"/>
-    <x v="80"/>
+    <n v="1.31"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-08-03 02:00:12"/>
     <x v="0"/>
-    <x v="14"/>
+    <n v="1.07"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-03-18 17:32:27"/>
     <x v="3"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-11-26 02:04:16"/>
     <x v="5"/>
-    <x v="81"/>
+    <n v="2.25"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-04-23 02:33:43"/>
     <x v="7"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-09-30 19:12:35"/>
     <x v="5"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-11-14 22:56:47"/>
     <x v="3"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="92"/>
     <s v="2023-09-21 18:20:46"/>
     <x v="3"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-06-26 01:56:20"/>
     <x v="3"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-04-13 19:04:30"/>
     <x v="5"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="2"/>
     <s v="2023-01-16 09:00:21"/>
     <x v="4"/>
-    <x v="83"/>
+    <n v="2.48"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-05-13 22:12:32"/>
     <x v="1"/>
-    <x v="84"/>
+    <n v="1.45"/>
   </r>
   <r>
     <n v="73"/>
     <s v="2023-03-10 00:04:50"/>
     <x v="3"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-05-27 11:29:34"/>
     <x v="3"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-10-11 14:05:32"/>
     <x v="3"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-03-28 22:44:58"/>
     <x v="3"/>
-    <x v="14"/>
+    <n v="1.07"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-12-24 08:13:59"/>
     <x v="3"/>
-    <x v="87"/>
+    <n v="1.22"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-03-05 01:28:28"/>
     <x v="1"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-07-11 13:38:06"/>
     <x v="5"/>
-    <x v="73"/>
+    <n v="1.87"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-01-31 02:35:52"/>
     <x v="5"/>
-    <x v="49"/>
+    <n v="2.56"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-08-31 00:47:21"/>
     <x v="0"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-05-08 00:16:22"/>
     <x v="0"/>
-    <x v="88"/>
+    <n v="2.73"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-08-18 11:23:24"/>
     <x v="6"/>
-    <x v="19"/>
+    <n v="2.69"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-08-11 15:06:24"/>
     <x v="6"/>
-    <x v="31"/>
+    <n v="1.32"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-02-08 10:51:57"/>
     <x v="3"/>
-    <x v="89"/>
+    <n v="2.57"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-10-13 12:20:33"/>
     <x v="3"/>
-    <x v="90"/>
+    <n v="1.6"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-08-12 16:59:54"/>
     <x v="1"/>
-    <x v="91"/>
+    <n v="2.97"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-12-05 16:34:26"/>
     <x v="7"/>
-    <x v="92"/>
+    <n v="1.56"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-01-22 16:04:30"/>
     <x v="1"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-03-30 20:29:17"/>
     <x v="4"/>
-    <x v="94"/>
+    <n v="2.0299999999999998"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-11-13 05:31:01"/>
     <x v="0"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-12-03 18:09:14"/>
     <x v="2"/>
-    <x v="80"/>
+    <n v="1.31"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-12-04 06:00:54"/>
     <x v="3"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-11-04 08:25:20"/>
     <x v="5"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-04-04 11:51:16"/>
     <x v="7"/>
-    <x v="37"/>
+    <n v="1.58"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-09-09 14:09:43"/>
     <x v="3"/>
-    <x v="96"/>
+    <n v="2.2599999999999998"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-01-21 04:15:27"/>
     <x v="3"/>
-    <x v="13"/>
+    <n v="1.82"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-05-11 04:34:18"/>
     <x v="5"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-08-03 18:41:31"/>
     <x v="3"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-01-24 23:41:06"/>
     <x v="2"/>
-    <x v="3"/>
+    <n v="2.36"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-06-09 03:10:54"/>
     <x v="7"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-09-26 12:47:12"/>
     <x v="1"/>
-    <x v="58"/>
+    <n v="1.36"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-10-12 03:54:53"/>
     <x v="0"/>
-    <x v="98"/>
+    <n v="2.33"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-08-27 18:41:02"/>
     <x v="3"/>
-    <x v="99"/>
+    <n v="2.6"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-11-20 03:31:55"/>
     <x v="4"/>
-    <x v="37"/>
+    <n v="1.58"/>
   </r>
   <r>
     <n v="13"/>
     <s v="2023-12-08 07:53:32"/>
     <x v="6"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="63"/>
     <s v="2023-01-17 22:16:54"/>
     <x v="6"/>
-    <x v="9"/>
+    <n v="1.1299999999999999"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-11-07 18:54:37"/>
     <x v="0"/>
-    <x v="15"/>
+    <n v="1.51"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-02-19 19:16:39"/>
     <x v="3"/>
-    <x v="18"/>
+    <n v="1.92"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-09-26 02:42:22"/>
     <x v="2"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-08-14 05:33:10"/>
     <x v="0"/>
-    <x v="100"/>
+    <n v="1.1599999999999999"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-04-18 16:16:10"/>
     <x v="4"/>
-    <x v="101"/>
+    <n v="1.1100000000000001"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-03-22 14:49:49"/>
     <x v="3"/>
-    <x v="102"/>
+    <n v="1.38"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-04-16 19:20:12"/>
     <x v="3"/>
-    <x v="103"/>
+    <n v="1.89"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-03-23 04:55:39"/>
     <x v="6"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-08-20 18:49:08"/>
     <x v="0"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-07-13 04:43:15"/>
     <x v="6"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-04-16 18:35:35"/>
     <x v="1"/>
-    <x v="105"/>
+    <n v="1.5"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-07-20 22:17:12"/>
     <x v="2"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-10-25 15:33:12"/>
     <x v="2"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-01-01 18:41:01"/>
     <x v="7"/>
-    <x v="106"/>
+    <n v="2.16"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-05-15 00:26:02"/>
     <x v="5"/>
-    <x v="107"/>
+    <n v="2.38"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-01-13 18:20:49"/>
     <x v="1"/>
-    <x v="108"/>
+    <n v="2.95"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-06-20 10:30:45"/>
     <x v="4"/>
-    <x v="109"/>
+    <n v="2.82"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-11-26 14:04:59"/>
     <x v="6"/>
-    <x v="110"/>
+    <n v="2.7"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-06-27 17:03:47"/>
     <x v="3"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-12-26 17:38:55"/>
     <x v="0"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-02-07 02:11:52"/>
     <x v="1"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-03-01 04:06:23"/>
     <x v="5"/>
-    <x v="112"/>
+    <n v="2.66"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-03-13 04:58:10"/>
     <x v="7"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-08-08 04:49:07"/>
     <x v="0"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-09-06 07:39:24"/>
     <x v="6"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-01-03 08:09:44"/>
     <x v="0"/>
-    <x v="5"/>
+    <n v="1.86"/>
   </r>
   <r>
     <n v="59"/>
     <s v="2023-05-12 04:58:13"/>
     <x v="2"/>
-    <x v="36"/>
+    <n v="2.85"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-01-26 15:51:31"/>
     <x v="4"/>
-    <x v="110"/>
+    <n v="2.7"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-03-29 17:39:41"/>
     <x v="5"/>
-    <x v="114"/>
+    <n v="2.2200000000000002"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-04-01 09:35:29"/>
     <x v="3"/>
-    <x v="14"/>
+    <n v="1.07"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-03-25 23:40:28"/>
     <x v="2"/>
-    <x v="115"/>
+    <n v="1.64"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-12-10 18:38:45"/>
     <x v="0"/>
-    <x v="116"/>
+    <n v="2.2400000000000002"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-04-07 11:00:07"/>
     <x v="3"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="44"/>
     <s v="2023-11-11 07:23:08"/>
     <x v="6"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-08-20 04:39:46"/>
     <x v="7"/>
-    <x v="71"/>
+    <n v="2.39"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-02-07 02:15:48"/>
     <x v="7"/>
-    <x v="2"/>
+    <n v="2.61"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-06-18 14:01:57"/>
     <x v="7"/>
-    <x v="118"/>
+    <n v="2.4900000000000002"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-06-05 20:29:29"/>
     <x v="1"/>
-    <x v="119"/>
+    <n v="1.23"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-10-12 11:56:19"/>
     <x v="4"/>
-    <x v="94"/>
+    <n v="2.0299999999999998"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-11-07 18:34:51"/>
     <x v="2"/>
-    <x v="56"/>
+    <n v="2.9"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-11-30 13:05:23"/>
     <x v="4"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-02-14 23:07:22"/>
     <x v="7"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-12-27 21:13:20"/>
     <x v="5"/>
-    <x v="44"/>
+    <n v="2.5499999999999998"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-06-26 02:36:25"/>
     <x v="1"/>
-    <x v="120"/>
+    <n v="2.11"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-08-08 12:17:06"/>
     <x v="3"/>
-    <x v="103"/>
+    <n v="1.89"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-07-19 06:31:43"/>
     <x v="1"/>
-    <x v="121"/>
+    <n v="2.77"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-10-19 14:51:54"/>
     <x v="2"/>
-    <x v="119"/>
+    <n v="1.23"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-06-21 11:31:03"/>
     <x v="1"/>
-    <x v="122"/>
+    <n v="2.4700000000000002"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-11-23 14:10:01"/>
     <x v="1"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-02-08 06:05:25"/>
     <x v="7"/>
-    <x v="25"/>
+    <n v="2.93"/>
   </r>
   <r>
     <n v="59"/>
     <s v="2023-02-02 06:14:36"/>
     <x v="5"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="63"/>
     <s v="2023-12-28 06:50:46"/>
     <x v="3"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-01-25 21:45:12"/>
     <x v="7"/>
-    <x v="123"/>
+    <n v="1"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-06-09 01:35:54"/>
     <x v="2"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-06-17 03:49:20"/>
     <x v="3"/>
-    <x v="125"/>
+    <n v="1.27"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-09-20 13:35:14"/>
     <x v="0"/>
-    <x v="70"/>
+    <n v="1.1000000000000001"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-08-02 19:23:45"/>
     <x v="1"/>
-    <x v="118"/>
+    <n v="2.4900000000000002"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-12-24 22:21:47"/>
     <x v="5"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-10-18 12:57:44"/>
     <x v="2"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-06-11 00:49:10"/>
     <x v="2"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-09-15 18:40:27"/>
     <x v="4"/>
-    <x v="39"/>
+    <n v="1.93"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-12-18 10:52:11"/>
     <x v="5"/>
-    <x v="126"/>
+    <n v="2.2999999999999998"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-11-21 10:00:04"/>
     <x v="4"/>
-    <x v="52"/>
+    <n v="2.35"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-07-02 13:16:19"/>
     <x v="2"/>
-    <x v="79"/>
+    <n v="1.84"/>
   </r>
   <r>
     <n v="63"/>
     <s v="2023-04-16 03:36:08"/>
     <x v="7"/>
-    <x v="116"/>
+    <n v="2.2400000000000002"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-07-18 10:48:19"/>
     <x v="3"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-01-17 09:33:36"/>
     <x v="6"/>
-    <x v="122"/>
+    <n v="2.4700000000000002"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-08-04 13:49:44"/>
     <x v="6"/>
-    <x v="109"/>
+    <n v="2.82"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-12-10 22:06:12"/>
     <x v="1"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-08-04 04:09:26"/>
     <x v="1"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-11-26 03:40:45"/>
     <x v="5"/>
-    <x v="128"/>
+    <n v="2.13"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-06-25 07:06:26"/>
     <x v="5"/>
-    <x v="114"/>
+    <n v="2.2200000000000002"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-03-28 18:10:47"/>
     <x v="5"/>
-    <x v="129"/>
+    <n v="1.59"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-08-26 14:58:04"/>
     <x v="4"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-06-23 11:11:19"/>
     <x v="6"/>
-    <x v="108"/>
+    <n v="2.95"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-05-11 18:47:14"/>
     <x v="0"/>
-    <x v="18"/>
+    <n v="1.92"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-08-22 00:59:43"/>
     <x v="3"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-05-02 01:03:20"/>
     <x v="1"/>
-    <x v="130"/>
+    <n v="1.01"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-10-14 21:26:40"/>
     <x v="4"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-11-18 22:07:40"/>
     <x v="0"/>
-    <x v="25"/>
+    <n v="2.93"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-12-26 20:38:25"/>
     <x v="1"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-05-17 00:45:52"/>
     <x v="2"/>
-    <x v="47"/>
+    <n v="1.24"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-05-25 14:42:33"/>
     <x v="5"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-05-04 21:22:30"/>
     <x v="0"/>
-    <x v="19"/>
+    <n v="2.69"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-03-04 03:17:26"/>
     <x v="3"/>
-    <x v="131"/>
+    <n v="2.86"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-06-19 09:34:29"/>
     <x v="7"/>
-    <x v="77"/>
+    <n v="2.63"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-01-17 06:12:28"/>
     <x v="3"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-01-18 14:28:09"/>
     <x v="3"/>
-    <x v="77"/>
+    <n v="2.63"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-08-31 01:51:11"/>
     <x v="5"/>
-    <x v="132"/>
+    <n v="2.79"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-03-18 02:08:51"/>
     <x v="4"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-10-27 15:57:21"/>
     <x v="6"/>
-    <x v="133"/>
+    <n v="2.12"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-07-23 14:01:11"/>
     <x v="2"/>
-    <x v="134"/>
+    <n v="1.7"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-02-20 13:57:34"/>
     <x v="4"/>
-    <x v="135"/>
+    <n v="2.46"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-04-06 09:21:03"/>
     <x v="0"/>
-    <x v="136"/>
+    <n v="3"/>
   </r>
   <r>
     <n v="2"/>
     <s v="2023-11-20 11:40:21"/>
     <x v="1"/>
-    <x v="22"/>
+    <n v="2.78"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-04-13 18:31:16"/>
     <x v="5"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-02-02 21:18:30"/>
     <x v="2"/>
-    <x v="121"/>
+    <n v="2.77"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-12-24 12:03:47"/>
     <x v="1"/>
-    <x v="137"/>
+    <n v="2.88"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-06-28 20:04:20"/>
     <x v="3"/>
-    <x v="92"/>
+    <n v="1.56"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-05-10 23:40:58"/>
     <x v="4"/>
-    <x v="138"/>
+    <n v="2.17"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-11-22 05:09:32"/>
     <x v="3"/>
-    <x v="139"/>
+    <n v="1.08"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-09-10 13:15:27"/>
     <x v="3"/>
-    <x v="133"/>
+    <n v="2.12"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-08-08 03:26:06"/>
     <x v="5"/>
-    <x v="36"/>
+    <n v="2.85"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-01-11 23:03:44"/>
     <x v="5"/>
-    <x v="37"/>
+    <n v="1.58"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-05-09 22:31:08"/>
     <x v="4"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-05-12 12:01:28"/>
     <x v="1"/>
-    <x v="140"/>
+    <n v="2.64"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-10-03 09:39:49"/>
     <x v="1"/>
-    <x v="141"/>
+    <n v="1.05"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-04-18 18:08:33"/>
     <x v="6"/>
-    <x v="40"/>
+    <n v="2.34"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-06-16 06:16:25"/>
     <x v="3"/>
-    <x v="138"/>
+    <n v="2.17"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-10-03 05:06:53"/>
     <x v="5"/>
-    <x v="116"/>
+    <n v="2.2400000000000002"/>
   </r>
   <r>
     <n v="73"/>
     <s v="2023-09-05 19:59:50"/>
     <x v="6"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-10-20 15:45:54"/>
     <x v="0"/>
-    <x v="48"/>
+    <n v="2.71"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-09-06 14:47:19"/>
     <x v="0"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-12-23 21:35:37"/>
     <x v="7"/>
-    <x v="76"/>
+    <n v="2.42"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-07-25 16:33:39"/>
     <x v="0"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-08-11 22:03:15"/>
     <x v="1"/>
-    <x v="143"/>
+    <n v="1.62"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-09-21 05:30:03"/>
     <x v="2"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-04-08 00:27:17"/>
     <x v="7"/>
-    <x v="115"/>
+    <n v="1.64"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-04-15 03:49:54"/>
     <x v="5"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-11-22 10:34:25"/>
     <x v="4"/>
-    <x v="50"/>
+    <n v="2.52"/>
   </r>
   <r>
     <n v="73"/>
     <s v="2023-12-03 07:07:43"/>
     <x v="7"/>
-    <x v="144"/>
+    <n v="1.63"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-07-29 23:00:20"/>
     <x v="5"/>
-    <x v="145"/>
+    <n v="1.41"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-07-07 06:15:27"/>
     <x v="6"/>
-    <x v="146"/>
+    <n v="1.3"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-02-10 03:24:26"/>
     <x v="4"/>
-    <x v="147"/>
+    <n v="2.21"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-09-06 21:07:37"/>
     <x v="1"/>
-    <x v="126"/>
+    <n v="2.2999999999999998"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-05-14 18:47:07"/>
     <x v="0"/>
-    <x v="148"/>
+    <n v="2.54"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-08-16 23:44:57"/>
     <x v="0"/>
-    <x v="65"/>
+    <n v="1.66"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-03-08 05:29:46"/>
     <x v="4"/>
-    <x v="149"/>
+    <n v="1.83"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-02-18 14:44:49"/>
     <x v="0"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-10-10 10:15:21"/>
     <x v="1"/>
-    <x v="77"/>
+    <n v="2.63"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-04-26 04:08:39"/>
     <x v="0"/>
-    <x v="131"/>
+    <n v="2.86"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-02-28 16:42:38"/>
     <x v="7"/>
-    <x v="108"/>
+    <n v="2.95"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-04-11 13:54:09"/>
     <x v="4"/>
-    <x v="121"/>
+    <n v="2.77"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-07-20 03:05:50"/>
     <x v="1"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-02-06 03:43:20"/>
     <x v="7"/>
-    <x v="150"/>
+    <n v="2.84"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-09-29 20:21:37"/>
     <x v="5"/>
-    <x v="129"/>
+    <n v="1.59"/>
   </r>
   <r>
     <n v="15"/>
     <s v="2023-01-16 21:40:37"/>
     <x v="5"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-03-19 21:33:14"/>
     <x v="0"/>
-    <x v="118"/>
+    <n v="2.4900000000000002"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-05-06 10:08:27"/>
     <x v="6"/>
-    <x v="151"/>
+    <n v="1.18"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-06-08 13:53:06"/>
     <x v="6"/>
-    <x v="99"/>
+    <n v="2.6"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-10-08 11:13:43"/>
     <x v="1"/>
-    <x v="52"/>
+    <n v="2.35"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-08-18 20:25:22"/>
     <x v="2"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-12-21 03:10:34"/>
     <x v="2"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-05-10 17:19:45"/>
     <x v="2"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-03-28 09:43:21"/>
     <x v="1"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-07-31 11:49:10"/>
     <x v="5"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-09-06 08:35:53"/>
     <x v="7"/>
-    <x v="58"/>
+    <n v="1.36"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-02-13 00:52:25"/>
     <x v="2"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="15"/>
     <s v="2023-01-18 01:15:24"/>
     <x v="6"/>
-    <x v="94"/>
+    <n v="2.0299999999999998"/>
   </r>
   <r>
     <n v="63"/>
     <s v="2023-10-10 17:34:32"/>
     <x v="1"/>
-    <x v="38"/>
+    <n v="1.91"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-09-16 20:53:48"/>
     <x v="3"/>
-    <x v="71"/>
+    <n v="2.39"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-05-11 07:51:58"/>
     <x v="3"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-02-24 15:50:36"/>
     <x v="0"/>
-    <x v="154"/>
+    <n v="2.81"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-12-05 22:07:22"/>
     <x v="1"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-10-12 18:41:05"/>
     <x v="3"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-04-02 04:02:57"/>
     <x v="6"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-08-26 02:46:37"/>
     <x v="6"/>
-    <x v="156"/>
+    <n v="1.76"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-09-04 02:37:45"/>
     <x v="5"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-08-16 22:20:17"/>
     <x v="6"/>
-    <x v="110"/>
+    <n v="2.7"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-09-14 15:25:29"/>
     <x v="3"/>
-    <x v="77"/>
+    <n v="2.63"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-06-22 06:39:16"/>
     <x v="7"/>
-    <x v="157"/>
+    <n v="1.61"/>
   </r>
   <r>
     <n v="48"/>
     <s v="2023-04-13 11:02:01"/>
     <x v="6"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-11-11 22:17:24"/>
     <x v="7"/>
-    <x v="158"/>
+    <n v="2.75"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-07-01 12:25:23"/>
     <x v="6"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-04-28 13:44:28"/>
     <x v="6"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-05-27 09:59:09"/>
     <x v="3"/>
-    <x v="159"/>
+    <n v="1.67"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-02-12 03:40:21"/>
     <x v="6"/>
-    <x v="106"/>
+    <n v="2.16"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-04-22 06:28:03"/>
     <x v="6"/>
-    <x v="12"/>
+    <n v="1.77"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-06-18 09:38:29"/>
     <x v="4"/>
-    <x v="154"/>
+    <n v="2.81"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-05-03 11:23:25"/>
     <x v="4"/>
-    <x v="76"/>
+    <n v="2.42"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-08-24 16:21:49"/>
     <x v="6"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-10-21 20:41:55"/>
     <x v="7"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-11-10 19:19:57"/>
     <x v="6"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-04-06 23:22:39"/>
     <x v="7"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-09-05 13:52:10"/>
     <x v="3"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-09-01 17:36:56"/>
     <x v="0"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-05-18 10:23:27"/>
     <x v="3"/>
-    <x v="114"/>
+    <n v="2.2200000000000002"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-07-02 09:03:13"/>
     <x v="5"/>
-    <x v="83"/>
+    <n v="2.48"/>
   </r>
   <r>
     <n v="59"/>
     <s v="2023-10-02 18:56:21"/>
     <x v="2"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-08-20 01:13:22"/>
     <x v="5"/>
-    <x v="12"/>
+    <n v="1.77"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-06-03 16:28:43"/>
     <x v="6"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-09-23 08:13:25"/>
     <x v="0"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-04-07 09:10:43"/>
     <x v="1"/>
-    <x v="88"/>
+    <n v="2.73"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-09-27 12:55:58"/>
     <x v="1"/>
-    <x v="160"/>
+    <n v="2.04"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-03-06 03:40:10"/>
     <x v="6"/>
-    <x v="114"/>
+    <n v="2.2200000000000002"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-10-10 23:02:17"/>
     <x v="6"/>
-    <x v="161"/>
+    <n v="2.4"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-10-31 02:31:04"/>
     <x v="1"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-10-11 05:49:23"/>
     <x v="6"/>
-    <x v="145"/>
+    <n v="1.41"/>
   </r>
   <r>
     <n v="80"/>
     <s v="2023-01-25 01:19:09"/>
     <x v="4"/>
-    <x v="138"/>
+    <n v="2.17"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-08-28 00:15:17"/>
     <x v="6"/>
-    <x v="87"/>
+    <n v="1.22"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-02-07 20:47:47"/>
     <x v="6"/>
-    <x v="139"/>
+    <n v="1.08"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-04-02 12:02:30"/>
     <x v="2"/>
-    <x v="45"/>
+    <n v="2.29"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-10-06 04:53:04"/>
     <x v="7"/>
-    <x v="101"/>
+    <n v="1.1100000000000001"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-03-20 15:41:42"/>
     <x v="3"/>
-    <x v="138"/>
+    <n v="2.17"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-07-29 02:55:17"/>
     <x v="5"/>
-    <x v="162"/>
+    <n v="1.94"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-10-20 15:41:54"/>
     <x v="0"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-10-23 04:06:31"/>
     <x v="0"/>
-    <x v="163"/>
+    <n v="2.15"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-01-15 14:47:47"/>
     <x v="3"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-05-05 05:57:58"/>
     <x v="2"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-03-26 21:08:56"/>
     <x v="4"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-04-24 23:05:41"/>
     <x v="0"/>
-    <x v="164"/>
+    <n v="2.09"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-06-26 15:33:08"/>
     <x v="6"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-06-04 10:57:25"/>
     <x v="6"/>
-    <x v="115"/>
+    <n v="1.64"/>
   </r>
   <r>
     <n v="15"/>
     <s v="2023-06-27 00:17:11"/>
     <x v="4"/>
-    <x v="131"/>
+    <n v="2.86"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-01-30 13:21:37"/>
     <x v="7"/>
-    <x v="5"/>
+    <n v="1.86"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-05-30 19:55:10"/>
     <x v="4"/>
-    <x v="165"/>
+    <n v="2.92"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-08-09 22:29:40"/>
     <x v="7"/>
-    <x v="56"/>
+    <n v="2.9"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-08-22 07:06:01"/>
     <x v="2"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-07-25 15:07:59"/>
     <x v="3"/>
-    <x v="96"/>
+    <n v="2.2599999999999998"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-01-29 12:21:13"/>
     <x v="1"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-03-06 14:22:45"/>
     <x v="1"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-03-26 05:57:15"/>
     <x v="6"/>
-    <x v="166"/>
+    <n v="2.27"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-10-23 11:58:58"/>
     <x v="4"/>
-    <x v="59"/>
+    <n v="1.33"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-11-10 19:47:06"/>
     <x v="4"/>
-    <x v="133"/>
+    <n v="2.12"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-03-15 09:28:14"/>
     <x v="2"/>
-    <x v="136"/>
+    <n v="3"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-10-21 02:05:30"/>
     <x v="7"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-05-25 16:04:52"/>
     <x v="6"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="32"/>
     <s v="2023-03-12 22:13:35"/>
     <x v="1"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-06-26 01:28:48"/>
     <x v="5"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-04-02 03:42:40"/>
     <x v="3"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-06-24 04:25:33"/>
     <x v="6"/>
-    <x v="45"/>
+    <n v="2.29"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-11-18 15:37:59"/>
     <x v="1"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-08-28 03:12:12"/>
     <x v="5"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-03-25 13:26:59"/>
     <x v="6"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-06-27 14:10:42"/>
     <x v="1"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-04-18 06:33:52"/>
     <x v="5"/>
-    <x v="167"/>
+    <n v="1.98"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-12-12 09:02:42"/>
     <x v="0"/>
-    <x v="84"/>
+    <n v="1.45"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-09-23 07:14:11"/>
     <x v="3"/>
-    <x v="100"/>
+    <n v="1.1599999999999999"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-07-01 07:43:03"/>
     <x v="6"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-05-28 21:23:20"/>
     <x v="7"/>
-    <x v="114"/>
+    <n v="2.2200000000000002"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-03-10 03:49:01"/>
     <x v="0"/>
-    <x v="37"/>
+    <n v="1.58"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-11-10 11:49:53"/>
     <x v="6"/>
-    <x v="168"/>
+    <n v="1.44"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-02-11 00:43:43"/>
     <x v="2"/>
-    <x v="81"/>
+    <n v="2.25"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-10-05 16:22:13"/>
     <x v="2"/>
-    <x v="145"/>
+    <n v="1.41"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-07-03 03:59:59"/>
     <x v="0"/>
-    <x v="89"/>
+    <n v="2.57"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-12-05 00:02:51"/>
     <x v="6"/>
-    <x v="151"/>
+    <n v="1.18"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-03-16 08:09:41"/>
     <x v="0"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-02-17 13:20:36"/>
     <x v="1"/>
-    <x v="35"/>
+    <n v="2.23"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-09-05 06:33:52"/>
     <x v="5"/>
-    <x v="118"/>
+    <n v="2.4900000000000002"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-02-10 21:44:16"/>
     <x v="3"/>
-    <x v="146"/>
+    <n v="1.3"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-02-28 04:13:10"/>
     <x v="2"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-10-19 10:50:53"/>
     <x v="6"/>
-    <x v="101"/>
+    <n v="1.1100000000000001"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-04-06 16:32:05"/>
     <x v="3"/>
-    <x v="52"/>
+    <n v="2.35"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-01-08 21:13:10"/>
     <x v="6"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="80"/>
     <s v="2023-10-17 14:15:40"/>
     <x v="1"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-05-27 05:08:26"/>
     <x v="5"/>
-    <x v="40"/>
+    <n v="2.34"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-02-01 18:17:24"/>
     <x v="7"/>
-    <x v="144"/>
+    <n v="1.63"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-01-17 17:12:45"/>
     <x v="4"/>
-    <x v="161"/>
+    <n v="2.4"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-04-23 10:47:10"/>
     <x v="0"/>
-    <x v="164"/>
+    <n v="2.09"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-04-06 06:01:17"/>
     <x v="7"/>
-    <x v="169"/>
+    <n v="2.0099999999999998"/>
   </r>
   <r>
     <n v="44"/>
     <s v="2023-02-02 07:10:03"/>
     <x v="3"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-09-20 16:47:58"/>
     <x v="4"/>
-    <x v="171"/>
+    <n v="1.73"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-06-11 16:46:48"/>
     <x v="0"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="48"/>
     <s v="2023-10-18 21:25:25"/>
     <x v="2"/>
-    <x v="71"/>
+    <n v="2.39"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-12-23 20:51:42"/>
     <x v="1"/>
-    <x v="172"/>
+    <n v="1.28"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-11-25 09:30:58"/>
     <x v="1"/>
-    <x v="89"/>
+    <n v="2.57"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-05-16 00:12:56"/>
     <x v="4"/>
-    <x v="39"/>
+    <n v="1.93"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-06-26 23:04:25"/>
     <x v="7"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-06-16 07:43:54"/>
     <x v="7"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-04-27 21:00:07"/>
     <x v="7"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-08-25 03:17:12"/>
     <x v="5"/>
-    <x v="34"/>
+    <n v="2.1"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-02-19 08:15:59"/>
     <x v="6"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="31"/>
     <s v="2023-05-27 11:43:44"/>
     <x v="2"/>
-    <x v="163"/>
+    <n v="2.15"/>
   </r>
   <r>
     <n v="44"/>
     <s v="2023-08-05 17:10:08"/>
     <x v="6"/>
-    <x v="1"/>
+    <n v="1.97"/>
   </r>
   <r>
     <n v="13"/>
     <s v="2023-03-09 00:30:58"/>
     <x v="2"/>
-    <x v="146"/>
+    <n v="1.3"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-03-19 21:21:00"/>
     <x v="6"/>
-    <x v="30"/>
+    <n v="1.96"/>
   </r>
   <r>
     <n v="31"/>
     <s v="2023-02-11 02:45:46"/>
     <x v="7"/>
-    <x v="40"/>
+    <n v="2.34"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-03-31 03:12:40"/>
     <x v="3"/>
-    <x v="154"/>
+    <n v="2.81"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-12-29 12:25:18"/>
     <x v="5"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-11-15 03:31:06"/>
     <x v="3"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-06-12 08:57:25"/>
     <x v="7"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-11-26 02:26:51"/>
     <x v="3"/>
-    <x v="44"/>
+    <n v="2.5499999999999998"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-04-05 22:55:19"/>
     <x v="7"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-08-18 09:10:08"/>
     <x v="2"/>
-    <x v="167"/>
+    <n v="1.98"/>
   </r>
   <r>
     <n v="13"/>
     <s v="2023-08-08 11:19:26"/>
     <x v="7"/>
-    <x v="30"/>
+    <n v="1.96"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-09-17 17:50:28"/>
     <x v="4"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-03-07 19:26:04"/>
     <x v="4"/>
-    <x v="135"/>
+    <n v="2.46"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-04-12 21:41:32"/>
     <x v="3"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-11-22 02:42:28"/>
     <x v="1"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-12-02 07:48:06"/>
     <x v="6"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="31"/>
     <s v="2023-06-02 06:11:38"/>
     <x v="2"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-11-03 00:17:56"/>
     <x v="7"/>
-    <x v="83"/>
+    <n v="2.48"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-10-25 01:19:06"/>
     <x v="3"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="44"/>
     <s v="2023-12-28 12:36:43"/>
     <x v="0"/>
-    <x v="173"/>
+    <n v="2.14"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-09-26 10:36:53"/>
     <x v="0"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-12-11 23:15:54"/>
     <x v="1"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-03-18 18:47:28"/>
     <x v="5"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-11-16 21:01:11"/>
     <x v="1"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-03-11 17:44:02"/>
     <x v="2"/>
-    <x v="15"/>
+    <n v="1.51"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-10-24 11:56:30"/>
     <x v="0"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-05-30 03:48:19"/>
     <x v="5"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-05-28 12:49:57"/>
     <x v="0"/>
-    <x v="79"/>
+    <n v="1.84"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-08-19 10:00:24"/>
     <x v="7"/>
-    <x v="174"/>
+    <n v="2"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-02-19 05:05:49"/>
     <x v="5"/>
-    <x v="175"/>
+    <n v="2.99"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-09-07 07:20:36"/>
     <x v="5"/>
-    <x v="176"/>
+    <n v="2.74"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-12-05 11:00:11"/>
     <x v="2"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-01-12 10:00:12"/>
     <x v="0"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-06-18 10:43:06"/>
     <x v="7"/>
-    <x v="164"/>
+    <n v="2.09"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-05-29 07:08:56"/>
     <x v="1"/>
-    <x v="154"/>
+    <n v="2.81"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-07-10 06:22:50"/>
     <x v="5"/>
-    <x v="38"/>
+    <n v="1.91"/>
   </r>
   <r>
     <n v="59"/>
     <s v="2023-06-23 11:15:37"/>
     <x v="6"/>
-    <x v="139"/>
+    <n v="1.08"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-12-18 06:36:24"/>
     <x v="6"/>
-    <x v="177"/>
+    <n v="1.72"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-05-16 19:28:48"/>
     <x v="6"/>
-    <x v="178"/>
+    <n v="2.0499999999999998"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-01-08 04:11:23"/>
     <x v="4"/>
-    <x v="158"/>
+    <n v="2.75"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-04-16 22:21:50"/>
     <x v="0"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-05-26 19:12:23"/>
     <x v="0"/>
-    <x v="133"/>
+    <n v="2.12"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-05-26 10:38:33"/>
     <x v="2"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-03-30 23:50:33"/>
     <x v="2"/>
-    <x v="175"/>
+    <n v="2.99"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-09-24 00:31:53"/>
     <x v="3"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-08-06 04:41:40"/>
     <x v="1"/>
-    <x v="160"/>
+    <n v="2.04"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-03-17 11:47:33"/>
     <x v="0"/>
-    <x v="35"/>
+    <n v="2.23"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-09-04 19:32:27"/>
     <x v="3"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-11-26 01:50:09"/>
     <x v="4"/>
-    <x v="106"/>
+    <n v="2.16"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-07-26 16:29:22"/>
     <x v="4"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-10-05 22:31:05"/>
     <x v="0"/>
-    <x v="172"/>
+    <n v="1.28"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-05-13 00:28:52"/>
     <x v="2"/>
-    <x v="179"/>
+    <n v="2.37"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-03-26 15:17:58"/>
     <x v="2"/>
-    <x v="180"/>
+    <n v="1.39"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-06-20 07:50:26"/>
     <x v="0"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-05-26 19:14:26"/>
     <x v="6"/>
-    <x v="123"/>
+    <n v="1"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-05-17 14:00:44"/>
     <x v="1"/>
-    <x v="158"/>
+    <n v="2.75"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-05-31 09:46:11"/>
     <x v="0"/>
-    <x v="181"/>
+    <n v="2.96"/>
   </r>
   <r>
     <n v="80"/>
     <s v="2023-02-06 02:26:57"/>
     <x v="6"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="73"/>
     <s v="2023-07-08 09:14:39"/>
     <x v="5"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="48"/>
     <s v="2023-11-07 10:25:15"/>
     <x v="3"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-08-26 07:00:49"/>
     <x v="1"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-01-02 13:39:59"/>
     <x v="3"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-04-18 16:53:26"/>
     <x v="5"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-10-10 00:07:26"/>
     <x v="3"/>
-    <x v="83"/>
+    <n v="2.48"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-10-25 12:37:54"/>
     <x v="3"/>
-    <x v="22"/>
+    <n v="2.78"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-05-19 07:13:53"/>
     <x v="6"/>
-    <x v="115"/>
+    <n v="1.64"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-02-26 21:04:05"/>
     <x v="3"/>
-    <x v="106"/>
+    <n v="2.16"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-03-08 21:51:39"/>
     <x v="6"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-09-16 06:54:56"/>
     <x v="7"/>
-    <x v="89"/>
+    <n v="2.57"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-05-24 08:33:57"/>
     <x v="5"/>
-    <x v="166"/>
+    <n v="2.27"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-02-27 11:03:57"/>
     <x v="2"/>
-    <x v="83"/>
+    <n v="2.48"/>
   </r>
   <r>
     <n v="92"/>
     <s v="2023-01-22 21:58:04"/>
     <x v="6"/>
-    <x v="36"/>
+    <n v="2.85"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-08-21 05:15:18"/>
     <x v="7"/>
-    <x v="140"/>
+    <n v="2.64"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-09-01 16:38:53"/>
     <x v="2"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-10-08 01:55:04"/>
     <x v="1"/>
-    <x v="81"/>
+    <n v="2.25"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-11-29 15:09:42"/>
     <x v="4"/>
-    <x v="182"/>
+    <n v="2.83"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-03-13 05:30:06"/>
     <x v="6"/>
-    <x v="136"/>
+    <n v="3"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-07-08 04:48:42"/>
     <x v="3"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-04-28 22:27:55"/>
     <x v="3"/>
-    <x v="65"/>
+    <n v="1.66"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-02-04 15:41:18"/>
     <x v="4"/>
-    <x v="45"/>
+    <n v="2.29"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-08-26 03:41:00"/>
     <x v="0"/>
-    <x v="128"/>
+    <n v="2.13"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-01-28 01:37:52"/>
     <x v="3"/>
-    <x v="103"/>
+    <n v="1.89"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-03-02 07:10:39"/>
     <x v="6"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-10-18 09:04:46"/>
     <x v="5"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-06-27 03:25:33"/>
     <x v="1"/>
-    <x v="183"/>
+    <n v="2.62"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-05-29 15:37:52"/>
     <x v="1"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-07-22 03:08:08"/>
     <x v="5"/>
-    <x v="122"/>
+    <n v="2.4700000000000002"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-12-05 10:46:33"/>
     <x v="5"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-01-21 09:24:28"/>
     <x v="7"/>
-    <x v="184"/>
+    <n v="2.3199999999999998"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-10-25 05:54:08"/>
     <x v="1"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-08-08 10:43:03"/>
     <x v="6"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-06-20 02:52:17"/>
     <x v="2"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-09-05 09:26:40"/>
     <x v="1"/>
-    <x v="48"/>
+    <n v="2.71"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-02-07 07:34:39"/>
     <x v="0"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-02-08 05:55:25"/>
     <x v="3"/>
-    <x v="185"/>
+    <n v="1.74"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-08-01 21:28:28"/>
     <x v="2"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-08-01 13:09:22"/>
     <x v="6"/>
-    <x v="147"/>
+    <n v="2.21"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-05-26 21:21:56"/>
     <x v="1"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-08-28 10:20:54"/>
     <x v="1"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-12-26 02:18:35"/>
     <x v="3"/>
-    <x v="173"/>
+    <n v="2.14"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-03-24 07:29:43"/>
     <x v="7"/>
-    <x v="186"/>
+    <n v="1.0900000000000001"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-08-31 21:55:35"/>
     <x v="1"/>
-    <x v="187"/>
+    <n v="1.79"/>
   </r>
   <r>
     <n v="92"/>
     <s v="2023-04-18 17:32:41"/>
     <x v="6"/>
-    <x v="78"/>
+    <n v="1.35"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-11-24 07:32:10"/>
     <x v="5"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-02-04 04:14:23"/>
     <x v="4"/>
-    <x v="188"/>
+    <n v="1.34"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-09-05 21:40:54"/>
     <x v="7"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-07-31 03:51:43"/>
     <x v="6"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="31"/>
     <s v="2023-11-09 06:19:23"/>
     <x v="1"/>
-    <x v="47"/>
+    <n v="1.24"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-04-17 23:11:19"/>
     <x v="0"/>
-    <x v="126"/>
+    <n v="2.2999999999999998"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-10-06 10:11:29"/>
     <x v="2"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-07-24 22:27:34"/>
     <x v="1"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-09-27 12:44:18"/>
     <x v="4"/>
-    <x v="108"/>
+    <n v="2.95"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-06-29 21:21:59"/>
     <x v="4"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-07-18 21:07:21"/>
     <x v="2"/>
-    <x v="108"/>
+    <n v="2.95"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-02-09 16:41:07"/>
     <x v="4"/>
-    <x v="6"/>
+    <n v="2.1800000000000002"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-07-02 02:37:26"/>
     <x v="7"/>
-    <x v="172"/>
+    <n v="1.28"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-06-20 08:39:18"/>
     <x v="4"/>
-    <x v="143"/>
+    <n v="1.62"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-03-21 07:07:35"/>
     <x v="7"/>
-    <x v="176"/>
+    <n v="2.74"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-11-20 05:06:23"/>
     <x v="6"/>
-    <x v="14"/>
+    <n v="1.07"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-08-12 12:51:38"/>
     <x v="1"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-09-13 22:35:59"/>
     <x v="4"/>
-    <x v="118"/>
+    <n v="2.4900000000000002"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-10-23 07:28:57"/>
     <x v="0"/>
-    <x v="137"/>
+    <n v="2.88"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-11-24 22:36:33"/>
     <x v="2"/>
-    <x v="140"/>
+    <n v="2.64"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-09-23 16:56:18"/>
     <x v="4"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-10-04 06:17:05"/>
     <x v="4"/>
-    <x v="143"/>
+    <n v="1.62"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-08-06 21:11:22"/>
     <x v="7"/>
-    <x v="77"/>
+    <n v="2.63"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-08-29 08:10:44"/>
     <x v="4"/>
-    <x v="98"/>
+    <n v="2.33"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-01-01 00:35:14"/>
     <x v="6"/>
-    <x v="161"/>
+    <n v="2.4"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-05-06 09:22:45"/>
     <x v="6"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-07-26 06:27:13"/>
     <x v="7"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-12-20 12:32:06"/>
     <x v="5"/>
-    <x v="101"/>
+    <n v="1.1100000000000001"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-11-19 07:43:02"/>
     <x v="2"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-08-04 22:58:41"/>
     <x v="1"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-12-15 00:40:07"/>
     <x v="0"/>
-    <x v="147"/>
+    <n v="2.21"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-02-26 15:38:43"/>
     <x v="5"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-08-26 16:20:43"/>
     <x v="7"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-06-05 09:22:27"/>
     <x v="3"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-09-25 04:24:45"/>
     <x v="5"/>
-    <x v="178"/>
+    <n v="2.0499999999999998"/>
   </r>
   <r>
     <n v="85"/>
     <s v="2023-12-02 22:17:44"/>
     <x v="5"/>
-    <x v="130"/>
+    <n v="1.01"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-12-02 20:37:58"/>
     <x v="2"/>
-    <x v="187"/>
+    <n v="1.79"/>
   </r>
   <r>
     <n v="80"/>
     <s v="2023-05-28 20:19:30"/>
     <x v="0"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-07-02 13:08:45"/>
     <x v="5"/>
-    <x v="9"/>
+    <n v="1.1299999999999999"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-04-05 00:28:17"/>
     <x v="7"/>
-    <x v="108"/>
+    <n v="2.95"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-04-18 10:14:08"/>
     <x v="1"/>
-    <x v="189"/>
+    <n v="2.58"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-05-02 02:59:00"/>
     <x v="4"/>
-    <x v="167"/>
+    <n v="1.98"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-12-29 21:06:58"/>
     <x v="6"/>
-    <x v="175"/>
+    <n v="2.99"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-12-20 02:36:18"/>
     <x v="0"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-08-31 03:25:32"/>
     <x v="4"/>
-    <x v="171"/>
+    <n v="1.73"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-09-04 16:04:05"/>
     <x v="4"/>
-    <x v="37"/>
+    <n v="1.58"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-09-19 22:38:17"/>
     <x v="2"/>
-    <x v="35"/>
+    <n v="2.23"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-02-11 15:35:57"/>
     <x v="6"/>
-    <x v="182"/>
+    <n v="2.83"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-02-10 18:38:40"/>
     <x v="6"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-02-09 19:30:16"/>
     <x v="1"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-04-26 10:24:43"/>
     <x v="4"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-03-14 03:58:39"/>
     <x v="3"/>
-    <x v="119"/>
+    <n v="1.23"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-10-18 10:19:11"/>
     <x v="3"/>
-    <x v="49"/>
+    <n v="2.56"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-10-12 09:02:51"/>
     <x v="7"/>
-    <x v="44"/>
+    <n v="2.5499999999999998"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-04-11 09:50:56"/>
     <x v="4"/>
-    <x v="61"/>
+    <n v="1.2"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-03-05 03:54:15"/>
     <x v="0"/>
-    <x v="161"/>
+    <n v="2.4"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-11-16 15:46:35"/>
     <x v="6"/>
-    <x v="115"/>
+    <n v="1.64"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-02-10 11:02:34"/>
     <x v="7"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-02-20 10:51:44"/>
     <x v="6"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="80"/>
     <s v="2023-10-05 22:20:23"/>
     <x v="7"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-09-25 06:17:48"/>
     <x v="2"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-06-22 17:03:55"/>
     <x v="0"/>
-    <x v="99"/>
+    <n v="2.6"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-05-05 21:42:52"/>
     <x v="4"/>
-    <x v="120"/>
+    <n v="2.11"/>
   </r>
   <r>
     <n v="32"/>
     <s v="2023-01-26 04:30:50"/>
     <x v="1"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-11-05 06:36:28"/>
     <x v="4"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-06-05 12:01:41"/>
     <x v="6"/>
-    <x v="89"/>
+    <n v="2.57"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-08-11 11:40:18"/>
     <x v="7"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-02-16 20:46:16"/>
     <x v="7"/>
-    <x v="178"/>
+    <n v="2.0499999999999998"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-10-09 03:46:01"/>
     <x v="2"/>
-    <x v="15"/>
+    <n v="1.51"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-10-03 16:43:11"/>
     <x v="5"/>
-    <x v="135"/>
+    <n v="2.46"/>
   </r>
   <r>
     <n v="17"/>
     <s v="2023-01-29 22:33:10"/>
     <x v="7"/>
-    <x v="109"/>
+    <n v="2.82"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-11-08 01:24:51"/>
     <x v="5"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-05-28 17:47:10"/>
     <x v="3"/>
-    <x v="90"/>
+    <n v="1.6"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-11-24 00:43:56"/>
     <x v="7"/>
-    <x v="44"/>
+    <n v="2.5499999999999998"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-06-15 07:13:16"/>
     <x v="1"/>
-    <x v="91"/>
+    <n v="2.97"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-12-26 02:43:24"/>
     <x v="1"/>
-    <x v="144"/>
+    <n v="1.63"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-12-08 14:15:19"/>
     <x v="0"/>
-    <x v="164"/>
+    <n v="2.09"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-06-12 06:42:56"/>
     <x v="4"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="92"/>
     <s v="2023-08-21 12:20:54"/>
     <x v="1"/>
-    <x v="190"/>
+    <n v="1.26"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-03-21 12:30:40"/>
     <x v="0"/>
-    <x v="40"/>
+    <n v="2.34"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-09-07 22:27:25"/>
     <x v="0"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="80"/>
     <s v="2023-09-01 21:32:38"/>
     <x v="6"/>
-    <x v="49"/>
+    <n v="2.56"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-04-22 19:33:30"/>
     <x v="3"/>
-    <x v="173"/>
+    <n v="2.14"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-06-07 16:12:10"/>
     <x v="3"/>
-    <x v="11"/>
+    <n v="1.25"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-11-20 09:53:38"/>
     <x v="7"/>
-    <x v="78"/>
+    <n v="1.35"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-04-16 02:31:06"/>
     <x v="0"/>
-    <x v="167"/>
+    <n v="1.98"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-12-09 18:50:52"/>
     <x v="2"/>
-    <x v="139"/>
+    <n v="1.08"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-11-25 01:59:35"/>
     <x v="7"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-11-07 04:29:36"/>
     <x v="3"/>
-    <x v="119"/>
+    <n v="1.23"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-03-01 10:42:13"/>
     <x v="5"/>
-    <x v="90"/>
+    <n v="1.6"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-04-19 16:56:56"/>
     <x v="0"/>
-    <x v="191"/>
+    <n v="2.65"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-03-17 11:13:10"/>
     <x v="6"/>
-    <x v="39"/>
+    <n v="1.93"/>
   </r>
   <r>
     <n v="32"/>
     <s v="2023-02-14 05:27:30"/>
     <x v="3"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-10-20 11:54:42"/>
     <x v="2"/>
-    <x v="188"/>
+    <n v="1.34"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-11-06 22:48:24"/>
     <x v="6"/>
-    <x v="185"/>
+    <n v="1.74"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-11-02 08:03:23"/>
     <x v="2"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-03-24 13:08:59"/>
     <x v="2"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-06-23 23:39:40"/>
     <x v="2"/>
-    <x v="103"/>
+    <n v="1.89"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-09-16 04:45:48"/>
     <x v="2"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-12-13 20:29:16"/>
     <x v="7"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-12-19 06:51:59"/>
     <x v="7"/>
-    <x v="185"/>
+    <n v="1.74"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-08-02 12:08:48"/>
     <x v="0"/>
-    <x v="192"/>
+    <n v="2.94"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-12-21 22:05:08"/>
     <x v="1"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-08-18 17:51:11"/>
     <x v="4"/>
-    <x v="171"/>
+    <n v="1.73"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-09-24 01:27:06"/>
     <x v="3"/>
-    <x v="159"/>
+    <n v="1.67"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-03-15 16:50:12"/>
     <x v="5"/>
-    <x v="112"/>
+    <n v="2.66"/>
   </r>
   <r>
     <n v="59"/>
     <s v="2023-09-07 04:47:21"/>
     <x v="1"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-02-01 20:49:20"/>
     <x v="2"/>
-    <x v="59"/>
+    <n v="1.33"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-08-16 05:58:42"/>
     <x v="1"/>
-    <x v="179"/>
+    <n v="2.37"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-06-03 22:52:14"/>
     <x v="5"/>
-    <x v="181"/>
+    <n v="2.96"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-11-21 09:21:37"/>
     <x v="2"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="92"/>
     <s v="2023-03-13 05:41:17"/>
     <x v="0"/>
-    <x v="106"/>
+    <n v="2.16"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-06-29 07:34:09"/>
     <x v="7"/>
-    <x v="107"/>
+    <n v="2.38"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-05-18 16:28:06"/>
     <x v="2"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-07-26 11:48:54"/>
     <x v="1"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-06-05 07:56:07"/>
     <x v="7"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-10-30 05:14:01"/>
     <x v="3"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-02-03 19:57:55"/>
     <x v="3"/>
-    <x v="92"/>
+    <n v="1.56"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-12-07 19:50:09"/>
     <x v="6"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-01-10 12:55:30"/>
     <x v="3"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-09-14 05:39:13"/>
     <x v="0"/>
-    <x v="47"/>
+    <n v="1.24"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-12-28 03:02:14"/>
     <x v="4"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-10-09 07:35:37"/>
     <x v="2"/>
-    <x v="167"/>
+    <n v="1.98"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-06-02 04:58:05"/>
     <x v="7"/>
-    <x v="105"/>
+    <n v="1.5"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-02-10 03:36:30"/>
     <x v="4"/>
-    <x v="21"/>
+    <n v="1.1399999999999999"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-12-27 05:01:14"/>
     <x v="6"/>
-    <x v="182"/>
+    <n v="2.83"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-01-07 22:32:22"/>
     <x v="5"/>
-    <x v="190"/>
+    <n v="1.26"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-11-03 11:16:06"/>
     <x v="2"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-01-28 04:28:43"/>
     <x v="3"/>
-    <x v="84"/>
+    <n v="1.45"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-05-15 21:53:26"/>
     <x v="7"/>
-    <x v="79"/>
+    <n v="1.84"/>
   </r>
   <r>
     <n v="93"/>
     <s v="2023-04-11 12:05:36"/>
     <x v="7"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-08-18 11:30:26"/>
     <x v="1"/>
-    <x v="169"/>
+    <n v="2.0099999999999998"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-04-05 14:59:55"/>
     <x v="5"/>
-    <x v="188"/>
+    <n v="1.34"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-10-27 20:22:29"/>
     <x v="5"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-08-07 03:45:08"/>
     <x v="3"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-11-02 18:27:25"/>
     <x v="5"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-06-04 06:31:11"/>
     <x v="3"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-04-18 16:36:09"/>
     <x v="7"/>
-    <x v="185"/>
+    <n v="1.74"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-11-18 23:55:07"/>
     <x v="3"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-05-07 05:26:11"/>
     <x v="7"/>
-    <x v="56"/>
+    <n v="2.9"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-10-11 04:52:13"/>
     <x v="2"/>
-    <x v="31"/>
+    <n v="1.32"/>
   </r>
   <r>
     <n v="48"/>
     <s v="2023-08-09 16:00:20"/>
     <x v="1"/>
-    <x v="121"/>
+    <n v="2.77"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-08-07 20:11:53"/>
     <x v="5"/>
-    <x v="172"/>
+    <n v="1.28"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-09-04 10:53:03"/>
     <x v="5"/>
-    <x v="103"/>
+    <n v="1.89"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-04-30 17:38:53"/>
     <x v="6"/>
-    <x v="35"/>
+    <n v="2.23"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-12-27 06:26:28"/>
     <x v="5"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="94"/>
     <s v="2023-07-29 18:41:16"/>
     <x v="7"/>
-    <x v="190"/>
+    <n v="1.26"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-09-11 02:26:51"/>
     <x v="4"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-11-28 22:19:10"/>
     <x v="1"/>
-    <x v="148"/>
+    <n v="2.54"/>
   </r>
   <r>
     <n v="13"/>
     <s v="2023-01-09 09:45:30"/>
     <x v="2"/>
-    <x v="193"/>
+    <n v="2.2000000000000002"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-04-02 01:54:16"/>
     <x v="4"/>
-    <x v="102"/>
+    <n v="1.38"/>
   </r>
   <r>
     <n v="32"/>
     <s v="2023-11-28 14:03:14"/>
     <x v="5"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-12-03 00:31:52"/>
     <x v="4"/>
-    <x v="182"/>
+    <n v="2.83"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-01-16 20:36:25"/>
     <x v="3"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-11-19 16:30:23"/>
     <x v="0"/>
-    <x v="194"/>
+    <n v="2.4300000000000002"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-02-01 00:04:26"/>
     <x v="7"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-05-09 23:06:59"/>
     <x v="2"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-01-18 20:09:19"/>
     <x v="2"/>
-    <x v="107"/>
+    <n v="2.38"/>
   </r>
   <r>
     <n v="21"/>
     <s v="2023-10-01 17:38:07"/>
     <x v="6"/>
-    <x v="53"/>
+    <n v="2.5"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-12-10 06:38:01"/>
     <x v="7"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-04-19 07:04:03"/>
     <x v="5"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-02-11 09:10:07"/>
     <x v="2"/>
-    <x v="80"/>
+    <n v="1.31"/>
   </r>
   <r>
     <n v="2"/>
     <s v="2023-03-01 13:23:02"/>
     <x v="3"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-12-17 00:41:57"/>
     <x v="4"/>
-    <x v="6"/>
+    <n v="2.1800000000000002"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-06-30 12:01:57"/>
     <x v="2"/>
-    <x v="162"/>
+    <n v="1.94"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-11-10 04:44:10"/>
     <x v="4"/>
-    <x v="178"/>
+    <n v="2.0499999999999998"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-04-30 08:28:36"/>
     <x v="6"/>
-    <x v="114"/>
+    <n v="2.2200000000000002"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-08-22 01:52:40"/>
     <x v="1"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-02-28 12:25:55"/>
     <x v="4"/>
-    <x v="39"/>
+    <n v="1.93"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-12-07 19:15:06"/>
     <x v="0"/>
-    <x v="139"/>
+    <n v="1.08"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-11-04 11:04:26"/>
     <x v="6"/>
-    <x v="43"/>
+    <n v="1.52"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-02-19 06:22:33"/>
     <x v="3"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-05-12 06:57:05"/>
     <x v="2"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-05-11 00:51:28"/>
     <x v="6"/>
-    <x v="87"/>
+    <n v="1.22"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-08-20 01:15:53"/>
     <x v="4"/>
-    <x v="91"/>
+    <n v="2.97"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-01-31 12:57:10"/>
     <x v="4"/>
-    <x v="9"/>
+    <n v="1.1299999999999999"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-05-16 01:59:28"/>
     <x v="1"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-08-17 23:31:17"/>
     <x v="4"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-03-31 07:22:14"/>
     <x v="2"/>
-    <x v="195"/>
+    <n v="1.47"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-04-28 08:32:10"/>
     <x v="1"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-09-14 16:11:04"/>
     <x v="6"/>
-    <x v="122"/>
+    <n v="2.4700000000000002"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-08-14 13:31:19"/>
     <x v="0"/>
-    <x v="176"/>
+    <n v="2.74"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-04-23 15:44:08"/>
     <x v="2"/>
-    <x v="147"/>
+    <n v="2.21"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-07-25 13:30:52"/>
     <x v="6"/>
-    <x v="167"/>
+    <n v="1.98"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-07-05 14:32:00"/>
     <x v="5"/>
-    <x v="18"/>
+    <n v="1.92"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-10-12 01:45:30"/>
     <x v="1"/>
-    <x v="50"/>
+    <n v="2.52"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-01-26 06:41:40"/>
     <x v="7"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-11-19 09:58:58"/>
     <x v="3"/>
-    <x v="166"/>
+    <n v="2.27"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-07-29 18:08:14"/>
     <x v="5"/>
-    <x v="34"/>
+    <n v="2.1"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-12-09 16:58:32"/>
     <x v="4"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-11-07 08:43:03"/>
     <x v="3"/>
-    <x v="25"/>
+    <n v="2.93"/>
   </r>
   <r>
     <n v="48"/>
     <s v="2023-05-07 11:07:31"/>
     <x v="1"/>
-    <x v="92"/>
+    <n v="1.56"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-08-28 04:02:52"/>
     <x v="2"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-08-27 12:16:13"/>
     <x v="5"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-06-20 05:33:31"/>
     <x v="7"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-02-15 12:51:09"/>
     <x v="2"/>
-    <x v="160"/>
+    <n v="2.04"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-08-09 04:49:56"/>
     <x v="2"/>
-    <x v="50"/>
+    <n v="2.52"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-06-10 03:18:10"/>
     <x v="2"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-07-14 16:24:44"/>
     <x v="0"/>
-    <x v="73"/>
+    <n v="1.87"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-07-31 11:21:59"/>
     <x v="1"/>
-    <x v="174"/>
+    <n v="2"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-07-12 03:14:31"/>
     <x v="7"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-01-30 11:34:22"/>
     <x v="4"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-04-01 05:20:02"/>
     <x v="6"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-07-29 14:19:41"/>
     <x v="2"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-09-20 18:10:29"/>
     <x v="5"/>
-    <x v="34"/>
+    <n v="2.1"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-11-17 00:01:35"/>
     <x v="6"/>
-    <x v="101"/>
+    <n v="1.1100000000000001"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-06-08 10:00:03"/>
     <x v="5"/>
-    <x v="2"/>
+    <n v="2.61"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-03-19 23:31:33"/>
     <x v="2"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-03-08 18:48:16"/>
     <x v="4"/>
-    <x v="160"/>
+    <n v="2.04"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-12-14 12:13:39"/>
     <x v="1"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-01-21 01:41:17"/>
     <x v="0"/>
-    <x v="87"/>
+    <n v="1.22"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-08-18 01:10:18"/>
     <x v="4"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-10-01 02:21:22"/>
     <x v="2"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-03-21 03:23:24"/>
     <x v="4"/>
-    <x v="19"/>
+    <n v="2.69"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-04-14 11:36:17"/>
     <x v="1"/>
-    <x v="56"/>
+    <n v="2.9"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-02-22 05:53:04"/>
     <x v="6"/>
-    <x v="81"/>
+    <n v="2.25"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-04-11 22:25:25"/>
     <x v="1"/>
-    <x v="183"/>
+    <n v="2.62"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-01-08 05:47:09"/>
     <x v="4"/>
-    <x v="146"/>
+    <n v="1.3"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-10-29 21:34:52"/>
     <x v="2"/>
-    <x v="119"/>
+    <n v="1.23"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-11-07 23:51:47"/>
     <x v="7"/>
-    <x v="163"/>
+    <n v="2.15"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-09-05 16:19:31"/>
     <x v="4"/>
-    <x v="192"/>
+    <n v="2.94"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-05-14 07:45:12"/>
     <x v="0"/>
-    <x v="59"/>
+    <n v="1.33"/>
   </r>
   <r>
     <n v="63"/>
     <s v="2023-05-14 06:13:51"/>
     <x v="2"/>
-    <x v="103"/>
+    <n v="1.89"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-03-09 03:20:58"/>
     <x v="1"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-06-01 19:23:26"/>
     <x v="1"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-12-18 09:12:37"/>
     <x v="3"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="32"/>
     <s v="2023-03-15 08:53:25"/>
     <x v="4"/>
-    <x v="70"/>
+    <n v="1.1000000000000001"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-07-20 10:41:20"/>
     <x v="4"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-06-04 13:42:29"/>
     <x v="5"/>
-    <x v="33"/>
+    <n v="1.68"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-12-19 21:46:17"/>
     <x v="6"/>
-    <x v="196"/>
+    <n v="1.17"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-12-05 11:20:23"/>
     <x v="3"/>
-    <x v="1"/>
+    <n v="1.97"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-02-03 06:00:34"/>
     <x v="2"/>
-    <x v="181"/>
+    <n v="2.96"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-12-27 08:44:23"/>
     <x v="4"/>
-    <x v="173"/>
+    <n v="2.14"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-02-22 18:58:43"/>
     <x v="7"/>
-    <x v="175"/>
+    <n v="2.99"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-12-11 11:03:41"/>
     <x v="5"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-01-29 11:00:17"/>
     <x v="1"/>
-    <x v="197"/>
+    <n v="1.55"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-07-08 11:17:11"/>
     <x v="6"/>
-    <x v="147"/>
+    <n v="2.21"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-11-29 09:53:57"/>
     <x v="0"/>
-    <x v="30"/>
+    <n v="1.96"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-08-14 03:41:12"/>
     <x v="5"/>
-    <x v="129"/>
+    <n v="1.59"/>
   </r>
   <r>
     <n v="46"/>
     <s v="2023-06-28 10:24:22"/>
     <x v="3"/>
-    <x v="189"/>
+    <n v="2.58"/>
   </r>
   <r>
     <n v="33"/>
     <s v="2023-06-17 03:36:18"/>
     <x v="0"/>
-    <x v="169"/>
+    <n v="2.0099999999999998"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-08-04 10:40:09"/>
     <x v="0"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-05-02 15:40:32"/>
     <x v="1"/>
-    <x v="187"/>
+    <n v="1.79"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-12-28 21:52:53"/>
     <x v="3"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-07-01 16:33:09"/>
     <x v="1"/>
-    <x v="135"/>
+    <n v="2.46"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-06-09 19:55:03"/>
     <x v="7"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-02-19 20:16:14"/>
     <x v="5"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-11-11 06:05:51"/>
     <x v="5"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-08-02 23:37:16"/>
     <x v="4"/>
-    <x v="40"/>
+    <n v="2.34"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-12-19 09:02:21"/>
     <x v="1"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-09-07 21:01:54"/>
     <x v="5"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-04-17 14:24:40"/>
     <x v="3"/>
-    <x v="32"/>
+    <n v="1.43"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-02-27 05:58:04"/>
     <x v="3"/>
-    <x v="182"/>
+    <n v="2.83"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-01-19 12:21:29"/>
     <x v="6"/>
-    <x v="31"/>
+    <n v="1.32"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-07-01 18:31:16"/>
     <x v="0"/>
-    <x v="88"/>
+    <n v="2.73"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-08-31 22:59:53"/>
     <x v="5"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-07-09 13:47:41"/>
     <x v="7"/>
-    <x v="94"/>
+    <n v="2.0299999999999998"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-08-17 23:55:35"/>
     <x v="1"/>
-    <x v="198"/>
+    <n v="2.06"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-02-12 00:13:32"/>
     <x v="0"/>
-    <x v="134"/>
+    <n v="1.7"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-03-09 15:09:07"/>
     <x v="4"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-12-18 13:04:50"/>
     <x v="6"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-02-19 12:04:12"/>
     <x v="7"/>
-    <x v="81"/>
+    <n v="2.25"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-01-28 19:44:04"/>
     <x v="2"/>
-    <x v="52"/>
+    <n v="2.35"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-09-09 22:40:38"/>
     <x v="7"/>
-    <x v="12"/>
+    <n v="1.77"/>
   </r>
   <r>
     <n v="100"/>
     <s v="2023-11-25 15:28:28"/>
     <x v="3"/>
-    <x v="141"/>
+    <n v="1.05"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-05-01 16:51:16"/>
     <x v="6"/>
-    <x v="13"/>
+    <n v="1.82"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-03-14 12:17:08"/>
     <x v="5"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-06-26 00:48:34"/>
     <x v="4"/>
-    <x v="173"/>
+    <n v="2.14"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-12-12 11:05:23"/>
     <x v="4"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-12-17 17:23:08"/>
     <x v="3"/>
-    <x v="61"/>
+    <n v="1.2"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-02-28 15:27:07"/>
     <x v="0"/>
-    <x v="181"/>
+    <n v="2.96"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-08-23 14:57:53"/>
     <x v="7"/>
-    <x v="198"/>
+    <n v="2.06"/>
   </r>
   <r>
     <n v="57"/>
     <s v="2023-07-02 00:55:14"/>
     <x v="4"/>
-    <x v="94"/>
+    <n v="2.0299999999999998"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-10-12 17:08:38"/>
     <x v="5"/>
-    <x v="106"/>
+    <n v="2.16"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-05-05 06:10:38"/>
     <x v="2"/>
-    <x v="122"/>
+    <n v="2.4700000000000002"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-10-02 14:43:20"/>
     <x v="0"/>
-    <x v="150"/>
+    <n v="2.84"/>
   </r>
   <r>
     <n v="65"/>
     <s v="2023-06-05 04:59:43"/>
     <x v="1"/>
-    <x v="49"/>
+    <n v="2.56"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-11-15 07:05:17"/>
     <x v="7"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-03-19 18:47:15"/>
     <x v="4"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-08-11 05:16:07"/>
     <x v="4"/>
-    <x v="94"/>
+    <n v="2.0299999999999998"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-07-29 18:06:00"/>
     <x v="4"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-09-14 12:25:22"/>
     <x v="3"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-09-21 02:44:34"/>
     <x v="7"/>
-    <x v="129"/>
+    <n v="1.59"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-10-17 15:41:34"/>
     <x v="7"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-10-08 21:00:40"/>
     <x v="3"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-10-12 11:23:46"/>
     <x v="3"/>
-    <x v="51"/>
+    <n v="1.46"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-09-10 17:27:16"/>
     <x v="1"/>
-    <x v="42"/>
+    <n v="1.37"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-02-19 14:25:53"/>
     <x v="3"/>
-    <x v="41"/>
+    <n v="2.08"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-05-06 08:27:12"/>
     <x v="5"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="86"/>
     <s v="2023-12-30 23:56:08"/>
     <x v="5"/>
-    <x v="98"/>
+    <n v="2.33"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-05-22 14:07:26"/>
     <x v="0"/>
-    <x v="193"/>
+    <n v="2.2000000000000002"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-10-12 21:09:38"/>
     <x v="5"/>
-    <x v="176"/>
+    <n v="2.74"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-03-14 02:21:17"/>
     <x v="5"/>
-    <x v="45"/>
+    <n v="2.29"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-06-04 11:15:30"/>
     <x v="3"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-05-29 18:23:36"/>
     <x v="6"/>
-    <x v="105"/>
+    <n v="1.5"/>
   </r>
   <r>
     <n v="67"/>
     <s v="2023-07-11 15:01:11"/>
     <x v="2"/>
-    <x v="196"/>
+    <n v="1.17"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-03-15 02:54:35"/>
     <x v="4"/>
-    <x v="126"/>
+    <n v="2.2999999999999998"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-12-04 10:47:14"/>
     <x v="1"/>
-    <x v="189"/>
+    <n v="2.58"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-06-06 18:11:16"/>
     <x v="2"/>
-    <x v="102"/>
+    <n v="1.38"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-08-06 06:09:05"/>
     <x v="7"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="93"/>
     <s v="2023-03-03 21:21:38"/>
     <x v="5"/>
-    <x v="7"/>
+    <n v="1.95"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-07-25 20:00:38"/>
     <x v="0"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-09-30 18:11:12"/>
     <x v="2"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-10-09 18:46:40"/>
     <x v="0"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="66"/>
     <s v="2023-03-24 09:09:26"/>
     <x v="6"/>
-    <x v="157"/>
+    <n v="1.61"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-11-24 15:24:32"/>
     <x v="7"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-01-29 15:50:30"/>
     <x v="5"/>
-    <x v="45"/>
+    <n v="2.29"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-08-30 19:00:03"/>
     <x v="5"/>
-    <x v="93"/>
+    <n v="2.89"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-04-28 16:12:24"/>
     <x v="7"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="91"/>
     <s v="2023-05-29 09:35:01"/>
     <x v="5"/>
-    <x v="11"/>
+    <n v="1.25"/>
   </r>
   <r>
     <n v="11"/>
     <s v="2023-11-03 22:58:16"/>
     <x v="7"/>
-    <x v="173"/>
+    <n v="2.14"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-07-15 11:47:34"/>
     <x v="6"/>
-    <x v="31"/>
+    <n v="1.32"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-12-01 11:59:27"/>
     <x v="3"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-11-25 13:31:18"/>
     <x v="2"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-09-24 04:57:05"/>
     <x v="6"/>
-    <x v="96"/>
+    <n v="2.2599999999999998"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-05-02 17:28:19"/>
     <x v="3"/>
-    <x v="115"/>
+    <n v="1.64"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-06-26 07:00:06"/>
     <x v="1"/>
-    <x v="170"/>
+    <n v="1.57"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-11-02 08:27:19"/>
     <x v="1"/>
-    <x v="55"/>
+    <n v="2.72"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-07-27 01:49:07"/>
     <x v="7"/>
-    <x v="38"/>
+    <n v="1.91"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-12-04 10:49:05"/>
     <x v="4"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-04-28 06:32:30"/>
     <x v="3"/>
-    <x v="68"/>
+    <n v="1.03"/>
   </r>
   <r>
     <n v="56"/>
     <s v="2023-01-24 17:45:33"/>
     <x v="3"/>
-    <x v="119"/>
+    <n v="1.23"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-03-26 15:27:47"/>
     <x v="6"/>
-    <x v="123"/>
+    <n v="1"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-02-26 18:48:26"/>
     <x v="6"/>
-    <x v="124"/>
+    <n v="1.85"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-07-16 14:49:51"/>
     <x v="1"/>
-    <x v="168"/>
+    <n v="1.44"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-05-09 18:00:19"/>
     <x v="5"/>
-    <x v="43"/>
+    <n v="1.52"/>
   </r>
   <r>
     <n v="30"/>
     <s v="2023-04-30 09:26:54"/>
     <x v="0"/>
-    <x v="78"/>
+    <n v="1.35"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-05-09 10:55:55"/>
     <x v="5"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-04-29 01:01:02"/>
     <x v="3"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="39"/>
     <s v="2023-03-14 20:34:53"/>
     <x v="0"/>
-    <x v="155"/>
+    <n v="2.59"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-06-17 11:00:55"/>
     <x v="1"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-07-25 04:20:21"/>
     <x v="2"/>
-    <x v="135"/>
+    <n v="2.46"/>
   </r>
   <r>
     <n v="4"/>
     <s v="2023-08-31 15:48:20"/>
     <x v="5"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-11-02 19:44:49"/>
     <x v="7"/>
-    <x v="154"/>
+    <n v="2.81"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-03-13 04:54:41"/>
     <x v="1"/>
-    <x v="158"/>
+    <n v="2.75"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-09-12 13:34:40"/>
     <x v="0"/>
-    <x v="191"/>
+    <n v="2.65"/>
   </r>
   <r>
     <n v="32"/>
     <s v="2023-05-30 06:38:24"/>
     <x v="3"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-08-17 12:57:44"/>
     <x v="6"/>
-    <x v="183"/>
+    <n v="2.62"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-09-11 00:29:49"/>
     <x v="6"/>
-    <x v="30"/>
+    <n v="1.96"/>
   </r>
   <r>
     <n v="43"/>
     <s v="2023-10-07 20:27:47"/>
     <x v="1"/>
-    <x v="143"/>
+    <n v="1.62"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-06-14 02:01:38"/>
     <x v="6"/>
-    <x v="138"/>
+    <n v="2.17"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-12-25 11:45:05"/>
     <x v="6"/>
-    <x v="197"/>
+    <n v="1.55"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-04-02 01:42:26"/>
     <x v="5"/>
-    <x v="24"/>
+    <n v="2.02"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-02-04 10:08:54"/>
     <x v="3"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-03-04 03:54:23"/>
     <x v="4"/>
-    <x v="5"/>
+    <n v="1.86"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-02-02 03:00:27"/>
     <x v="2"/>
-    <x v="69"/>
+    <n v="1.8"/>
   </r>
   <r>
     <n v="95"/>
     <s v="2023-07-12 05:07:23"/>
     <x v="1"/>
-    <x v="71"/>
+    <n v="2.39"/>
   </r>
   <r>
     <n v="54"/>
     <s v="2023-04-26 21:10:08"/>
     <x v="7"/>
-    <x v="71"/>
+    <n v="2.39"/>
   </r>
   <r>
     <n v="60"/>
     <s v="2023-01-05 09:57:01"/>
     <x v="7"/>
-    <x v="185"/>
+    <n v="1.74"/>
   </r>
   <r>
     <n v="19"/>
     <s v="2023-06-30 02:14:15"/>
     <x v="6"/>
-    <x v="3"/>
+    <n v="2.36"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-10-09 03:17:06"/>
     <x v="3"/>
-    <x v="111"/>
+    <n v="1.9"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-05-19 10:34:09"/>
     <x v="2"/>
-    <x v="84"/>
+    <n v="1.45"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-12-03 01:36:43"/>
     <x v="6"/>
-    <x v="61"/>
+    <n v="1.2"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-07-21 07:15:24"/>
     <x v="2"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-07-20 18:14:30"/>
     <x v="1"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-03-15 22:58:26"/>
     <x v="7"/>
-    <x v="16"/>
+    <n v="2.91"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-01-03 15:00:36"/>
     <x v="3"/>
-    <x v="168"/>
+    <n v="1.44"/>
   </r>
   <r>
     <n v="34"/>
     <s v="2023-05-15 00:53:16"/>
     <x v="5"/>
-    <x v="64"/>
+    <n v="1.29"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-05-11 20:21:37"/>
     <x v="3"/>
-    <x v="180"/>
+    <n v="1.39"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-05-15 23:14:28"/>
     <x v="1"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-01-07 18:03:43"/>
     <x v="6"/>
-    <x v="160"/>
+    <n v="2.04"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-01-30 13:11:58"/>
     <x v="4"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-07-11 02:04:33"/>
     <x v="1"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-06-10 19:31:37"/>
     <x v="2"/>
-    <x v="125"/>
+    <n v="1.27"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-11-04 01:08:42"/>
     <x v="1"/>
-    <x v="151"/>
+    <n v="1.18"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-08-13 05:46:27"/>
     <x v="2"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-01-21 01:58:32"/>
     <x v="4"/>
-    <x v="130"/>
+    <n v="1.01"/>
   </r>
   <r>
     <n v="62"/>
     <s v="2023-12-10 11:10:37"/>
     <x v="2"/>
-    <x v="127"/>
+    <n v="1.06"/>
   </r>
   <r>
     <n v="84"/>
     <s v="2023-07-01 18:20:01"/>
     <x v="5"/>
-    <x v="81"/>
+    <n v="2.25"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-03-10 15:18:42"/>
     <x v="6"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="42"/>
     <s v="2023-08-28 10:13:51"/>
     <x v="7"/>
-    <x v="189"/>
+    <n v="2.58"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-08-30 12:07:47"/>
     <x v="1"/>
-    <x v="140"/>
+    <n v="2.64"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-04-30 17:17:11"/>
     <x v="2"/>
-    <x v="22"/>
+    <n v="2.78"/>
   </r>
   <r>
     <n v="18"/>
     <s v="2023-03-21 10:52:13"/>
     <x v="5"/>
-    <x v="76"/>
+    <n v="2.42"/>
   </r>
   <r>
     <n v="5"/>
     <s v="2023-10-13 14:43:05"/>
     <x v="3"/>
-    <x v="95"/>
+    <n v="1.1200000000000001"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-08-19 12:55:32"/>
     <x v="7"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="14"/>
     <s v="2023-10-31 21:02:00"/>
     <x v="2"/>
-    <x v="199"/>
+    <n v="1.48"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-11-17 10:13:32"/>
     <x v="1"/>
-    <x v="151"/>
+    <n v="1.18"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-11-20 02:40:28"/>
     <x v="7"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-08-05 17:12:25"/>
     <x v="2"/>
-    <x v="161"/>
+    <n v="2.4"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-01-09 04:42:35"/>
     <x v="0"/>
-    <x v="198"/>
+    <n v="2.06"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-12-11 23:25:51"/>
     <x v="3"/>
-    <x v="46"/>
+    <n v="1.19"/>
   </r>
   <r>
     <n v="37"/>
     <s v="2023-09-15 17:43:32"/>
     <x v="4"/>
-    <x v="3"/>
+    <n v="2.36"/>
   </r>
   <r>
     <n v="74"/>
     <s v="2023-02-20 15:15:38"/>
     <x v="1"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-02-03 15:42:32"/>
     <x v="2"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="69"/>
     <s v="2023-10-09 09:24:59"/>
     <x v="2"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="10"/>
     <s v="2023-11-29 20:29:37"/>
     <x v="7"/>
-    <x v="137"/>
+    <n v="2.88"/>
   </r>
   <r>
     <n v="51"/>
     <s v="2023-09-24 04:13:45"/>
     <x v="5"/>
-    <x v="47"/>
+    <n v="1.24"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-12-10 17:34:04"/>
     <x v="7"/>
-    <x v="76"/>
+    <n v="2.42"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-01-08 16:02:43"/>
     <x v="2"/>
-    <x v="63"/>
+    <n v="2.98"/>
   </r>
   <r>
     <n v="64"/>
     <s v="2023-12-25 20:19:16"/>
     <x v="7"/>
-    <x v="87"/>
+    <n v="1.22"/>
   </r>
   <r>
     <n v="73"/>
     <s v="2023-04-13 19:34:35"/>
     <x v="0"/>
-    <x v="75"/>
+    <n v="2.8"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-11-14 19:14:58"/>
     <x v="1"/>
-    <x v="112"/>
+    <n v="2.66"/>
   </r>
   <r>
     <n v="99"/>
     <s v="2023-02-02 13:26:53"/>
     <x v="6"/>
-    <x v="182"/>
+    <n v="2.83"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-03-10 07:51:14"/>
     <x v="6"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-09-16 16:29:46"/>
     <x v="3"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-08-30 08:38:18"/>
     <x v="0"/>
-    <x v="158"/>
+    <n v="2.75"/>
   </r>
   <r>
     <n v="81"/>
     <s v="2023-05-16 19:38:32"/>
     <x v="4"/>
-    <x v="135"/>
+    <n v="2.46"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-02-26 07:13:32"/>
     <x v="0"/>
-    <x v="184"/>
+    <n v="2.3199999999999998"/>
   </r>
   <r>
     <n v="27"/>
     <s v="2023-02-04 04:26:43"/>
     <x v="6"/>
-    <x v="67"/>
+    <n v="1.1499999999999999"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-09-22 16:03:54"/>
     <x v="0"/>
-    <x v="148"/>
+    <n v="2.54"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-08-26 02:45:36"/>
     <x v="5"/>
-    <x v="168"/>
+    <n v="1.44"/>
   </r>
   <r>
     <n v="53"/>
     <s v="2023-03-28 20:21:00"/>
     <x v="3"/>
-    <x v="190"/>
+    <n v="1.26"/>
   </r>
   <r>
     <n v="44"/>
     <s v="2023-10-06 22:18:53"/>
     <x v="5"/>
-    <x v="66"/>
+    <n v="1.54"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-10-16 13:01:04"/>
     <x v="5"/>
-    <x v="121"/>
+    <n v="2.77"/>
   </r>
   <r>
     <n v="50"/>
     <s v="2023-06-28 05:22:35"/>
     <x v="2"/>
-    <x v="12"/>
+    <n v="1.77"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-11-08 18:48:39"/>
     <x v="5"/>
-    <x v="89"/>
+    <n v="2.57"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-10-04 04:17:35"/>
     <x v="7"/>
-    <x v="20"/>
+    <n v="1.04"/>
   </r>
   <r>
     <n v="96"/>
     <s v="2023-09-09 17:22:47"/>
     <x v="1"/>
-    <x v="50"/>
+    <n v="2.52"/>
   </r>
   <r>
     <n v="97"/>
     <s v="2023-12-17 07:30:52"/>
     <x v="6"/>
-    <x v="60"/>
+    <n v="1.71"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-03-11 15:07:53"/>
     <x v="2"/>
-    <x v="193"/>
+    <n v="2.2000000000000002"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-02-11 14:11:31"/>
     <x v="0"/>
-    <x v="139"/>
+    <n v="1.08"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-09-10 17:55:56"/>
     <x v="7"/>
-    <x v="122"/>
+    <n v="2.4700000000000002"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-04-25 14:56:32"/>
     <x v="6"/>
-    <x v="8"/>
+    <n v="2.2799999999999998"/>
   </r>
   <r>
     <n v="2"/>
     <s v="2023-07-05 06:22:23"/>
     <x v="4"/>
-    <x v="13"/>
+    <n v="1.82"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-03-16 00:24:25"/>
     <x v="5"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-08-22 17:17:20"/>
     <x v="6"/>
-    <x v="192"/>
+    <n v="2.94"/>
   </r>
   <r>
     <n v="83"/>
     <s v="2023-09-02 22:57:32"/>
     <x v="5"/>
-    <x v="157"/>
+    <n v="1.61"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-08-16 00:43:42"/>
     <x v="5"/>
-    <x v="113"/>
+    <n v="1.21"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-10-16 15:05:12"/>
     <x v="0"/>
-    <x v="150"/>
+    <n v="2.84"/>
   </r>
   <r>
     <n v="75"/>
     <s v="2023-07-03 18:27:27"/>
     <x v="7"/>
-    <x v="28"/>
+    <n v="2.67"/>
   </r>
   <r>
     <n v="15"/>
     <s v="2023-11-17 04:50:57"/>
     <x v="1"/>
-    <x v="19"/>
+    <n v="2.69"/>
   </r>
   <r>
     <n v="71"/>
     <s v="2023-01-10 20:17:30"/>
     <x v="0"/>
-    <x v="23"/>
+    <n v="1.42"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-01-28 21:24:45"/>
     <x v="5"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-01-27 22:24:26"/>
     <x v="5"/>
-    <x v="195"/>
+    <n v="1.47"/>
   </r>
   <r>
     <n v="20"/>
     <s v="2023-08-14 21:12:50"/>
     <x v="5"/>
-    <x v="57"/>
+    <n v="2.41"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-06-25 15:26:22"/>
     <x v="1"/>
-    <x v="117"/>
+    <n v="1.99"/>
   </r>
   <r>
     <n v="7"/>
     <s v="2023-11-19 19:28:30"/>
     <x v="6"/>
-    <x v="159"/>
+    <n v="1.67"/>
   </r>
   <r>
     <n v="49"/>
     <s v="2023-03-29 09:47:17"/>
     <x v="4"/>
-    <x v="145"/>
+    <n v="1.41"/>
   </r>
   <r>
     <n v="1"/>
     <s v="2023-08-20 04:39:52"/>
     <x v="2"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-03-29 22:26:29"/>
     <x v="1"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="40"/>
     <s v="2023-03-09 08:24:22"/>
     <x v="2"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="82"/>
     <s v="2023-10-22 14:47:01"/>
     <x v="6"/>
-    <x v="17"/>
+    <n v="2.87"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-04-23 23:52:10"/>
     <x v="1"/>
-    <x v="47"/>
+    <n v="1.24"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-03-17 18:20:06"/>
     <x v="6"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="38"/>
     <s v="2023-07-08 09:39:51"/>
     <x v="3"/>
-    <x v="14"/>
+    <n v="1.07"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-12-04 23:40:33"/>
     <x v="3"/>
-    <x v="19"/>
+    <n v="2.69"/>
   </r>
   <r>
     <n v="28"/>
     <s v="2023-09-06 13:09:05"/>
     <x v="0"/>
-    <x v="196"/>
+    <n v="1.17"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-01-06 18:44:06"/>
     <x v="0"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="77"/>
     <s v="2023-05-06 10:30:10"/>
     <x v="1"/>
-    <x v="72"/>
+    <n v="2.76"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-01-10 05:33:31"/>
     <x v="3"/>
-    <x v="79"/>
+    <n v="1.84"/>
   </r>
   <r>
     <n v="45"/>
     <s v="2023-09-30 08:41:21"/>
     <x v="1"/>
-    <x v="4"/>
+    <n v="1.69"/>
   </r>
   <r>
     <n v="26"/>
     <s v="2023-12-25 02:56:37"/>
     <x v="5"/>
-    <x v="186"/>
+    <n v="1.0900000000000001"/>
   </r>
   <r>
     <n v="68"/>
     <s v="2023-02-10 16:14:01"/>
     <x v="4"/>
-    <x v="26"/>
+    <n v="2.4500000000000002"/>
   </r>
   <r>
     <n v="88"/>
     <s v="2023-01-02 02:26:23"/>
     <x v="0"/>
-    <x v="145"/>
+    <n v="1.41"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-03-21 01:10:42"/>
     <x v="5"/>
-    <x v="82"/>
+    <n v="1.88"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-06-05 17:16:58"/>
     <x v="0"/>
-    <x v="85"/>
+    <n v="1.78"/>
   </r>
   <r>
     <n v="59"/>
     <s v="2023-05-02 09:44:56"/>
     <x v="3"/>
-    <x v="142"/>
+    <n v="1.81"/>
   </r>
   <r>
     <n v="36"/>
     <s v="2023-04-03 10:54:24"/>
     <x v="5"/>
-    <x v="192"/>
+    <n v="2.94"/>
   </r>
   <r>
     <n v="52"/>
     <s v="2023-05-22 11:59:19"/>
     <x v="7"/>
-    <x v="13"/>
+    <n v="1.82"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-05-05 22:27:09"/>
     <x v="3"/>
-    <x v="0"/>
+    <n v="1.53"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-11-28 18:49:05"/>
     <x v="5"/>
-    <x v="175"/>
+    <n v="2.99"/>
   </r>
   <r>
     <n v="23"/>
     <s v="2023-08-26 04:35:27"/>
     <x v="4"/>
-    <x v="97"/>
+    <n v="1.75"/>
   </r>
   <r>
     <n v="24"/>
     <s v="2023-05-15 19:17:44"/>
     <x v="3"/>
-    <x v="100"/>
+    <n v="1.1599999999999999"/>
   </r>
   <r>
     <n v="8"/>
     <s v="2023-01-20 16:04:13"/>
     <x v="5"/>
-    <x v="151"/>
+    <n v="1.18"/>
   </r>
   <r>
     <n v="61"/>
     <s v="2023-04-14 15:42:02"/>
     <x v="5"/>
-    <x v="185"/>
+    <n v="1.74"/>
   </r>
   <r>
     <n v="6"/>
     <s v="2023-01-06 05:42:46"/>
     <x v="1"/>
-    <x v="200"/>
+    <n v="2.0699999999999998"/>
   </r>
   <r>
     <n v="90"/>
     <s v="2023-03-23 17:07:41"/>
     <x v="4"/>
-    <x v="9"/>
+    <n v="1.1299999999999999"/>
   </r>
   <r>
     <n v="47"/>
     <s v="2023-10-28 08:49:11"/>
     <x v="1"/>
-    <x v="104"/>
+    <n v="1.4"/>
   </r>
   <r>
     <n v="58"/>
     <s v="2023-01-23 13:52:30"/>
     <x v="0"/>
-    <x v="11"/>
+    <n v="1.25"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-04-12 14:46:04"/>
     <x v="4"/>
-    <x v="54"/>
+    <n v="2.5099999999999998"/>
   </r>
   <r>
     <n v="55"/>
     <s v="2023-10-02 19:48:54"/>
     <x v="5"/>
-    <x v="98"/>
+    <n v="2.33"/>
   </r>
   <r>
     <n v="41"/>
     <s v="2023-01-29 10:18:10"/>
     <x v="1"/>
-    <x v="141"/>
+    <n v="1.05"/>
   </r>
   <r>
     <n v="72"/>
     <s v="2023-12-02 05:00:19"/>
     <x v="5"/>
-    <x v="27"/>
+    <n v="2.5299999999999998"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-09-08 09:59:31"/>
     <x v="4"/>
-    <x v="31"/>
+    <n v="1.32"/>
   </r>
   <r>
     <n v="79"/>
     <s v="2023-05-18 03:55:11"/>
     <x v="2"/>
-    <x v="152"/>
+    <n v="2.31"/>
   </r>
   <r>
     <n v="12"/>
     <s v="2023-10-24 11:01:10"/>
     <x v="5"/>
-    <x v="25"/>
+    <n v="2.93"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-12-22 00:37:59"/>
     <x v="3"/>
-    <x v="112"/>
+    <n v="2.66"/>
   </r>
   <r>
     <n v="25"/>
     <s v="2023-11-28 07:42:20"/>
     <x v="7"/>
-    <x v="74"/>
+    <n v="1.02"/>
   </r>
   <r>
     <n v="70"/>
     <s v="2023-02-04 02:52:29"/>
     <x v="4"/>
-    <x v="88"/>
+    <n v="2.73"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-05-10 07:50:54"/>
     <x v="6"/>
-    <x v="143"/>
+    <n v="1.62"/>
   </r>
   <r>
     <n v="9"/>
     <s v="2023-02-28 17:41:31"/>
     <x v="1"/>
-    <x v="10"/>
+    <n v="1.65"/>
   </r>
   <r>
     <n v="98"/>
     <s v="2023-07-01 15:19:57"/>
     <x v="3"/>
-    <x v="192"/>
+    <n v="2.94"/>
   </r>
   <r>
     <n v="35"/>
     <s v="2023-11-26 18:22:55"/>
     <x v="7"/>
-    <x v="153"/>
+    <n v="1.49"/>
   </r>
   <r>
     <n v="29"/>
     <s v="2023-06-19 09:44:57"/>
     <x v="7"/>
-    <x v="193"/>
+    <n v="2.2000000000000002"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-06-11 09:39:28"/>
     <x v="0"/>
-    <x v="156"/>
+    <n v="1.76"/>
   </r>
   <r>
     <n v="76"/>
     <s v="2023-06-06 15:12:39"/>
     <x v="7"/>
-    <x v="166"/>
+    <n v="2.27"/>
   </r>
   <r>
     <n v="78"/>
     <s v="2023-10-29 02:02:15"/>
     <x v="0"/>
-    <x v="177"/>
+    <n v="1.72"/>
   </r>
   <r>
     <n v="16"/>
     <s v="2023-09-09 16:27:33"/>
     <x v="5"/>
-    <x v="36"/>
+    <n v="2.85"/>
   </r>
   <r>
     <n v="3"/>
     <s v="2023-05-03 18:59:11"/>
     <x v="1"/>
-    <x v="58"/>
+    <n v="1.36"/>
   </r>
   <r>
     <n v="87"/>
     <s v="2023-01-13 03:09:47"/>
     <x v="2"/>
-    <x v="29"/>
+    <n v="2.19"/>
   </r>
   <r>
     <n v="93"/>
     <s v="2023-07-16 12:11:35"/>
     <x v="4"/>
-    <x v="86"/>
+    <n v="2.68"/>
   </r>
   <r>
     <n v="22"/>
     <s v="2023-05-25 09:24:13"/>
     <x v="2"/>
-    <x v="166"/>
+    <n v="2.27"/>
   </r>
   <r>
     <n v="89"/>
     <s v="2023-10-08 09:06:33"/>
     <x v="0"/>
-    <x v="190"/>
+    <n v="1.26"/>
   </r>
   <r>
     <m/>
     <m/>
     <x v="8"/>
-    <x v="201"/>
+    <m/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表4" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="功能调用类型">
-  <location ref="I25:K34" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I14:K24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -9726,222 +9429,16 @@
         <item x="7"/>
         <item x="4"/>
         <item x="2"/>
-        <item h="1" x="8"/>
+        <item x="8"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="203">
-        <item x="123"/>
-        <item x="130"/>
-        <item x="74"/>
-        <item x="68"/>
-        <item x="20"/>
-        <item x="141"/>
-        <item x="127"/>
-        <item x="14"/>
-        <item x="139"/>
-        <item x="186"/>
-        <item x="70"/>
-        <item x="101"/>
-        <item x="95"/>
-        <item x="9"/>
-        <item x="21"/>
-        <item x="67"/>
-        <item x="100"/>
-        <item x="196"/>
-        <item x="151"/>
-        <item x="46"/>
-        <item x="61"/>
-        <item x="113"/>
-        <item x="87"/>
-        <item x="119"/>
-        <item x="47"/>
-        <item x="11"/>
-        <item x="190"/>
-        <item x="125"/>
-        <item x="172"/>
-        <item x="64"/>
-        <item x="146"/>
-        <item x="80"/>
-        <item x="31"/>
-        <item x="59"/>
-        <item x="188"/>
-        <item x="78"/>
-        <item x="58"/>
-        <item x="42"/>
-        <item x="102"/>
-        <item x="180"/>
-        <item x="104"/>
-        <item x="145"/>
-        <item x="23"/>
-        <item x="32"/>
-        <item x="168"/>
-        <item x="84"/>
-        <item x="51"/>
-        <item x="195"/>
-        <item x="199"/>
-        <item x="153"/>
-        <item x="105"/>
-        <item x="15"/>
-        <item x="43"/>
-        <item x="0"/>
-        <item x="66"/>
-        <item x="197"/>
-        <item x="92"/>
-        <item x="170"/>
-        <item x="37"/>
-        <item x="129"/>
-        <item x="90"/>
-        <item x="157"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="115"/>
-        <item x="10"/>
-        <item x="65"/>
-        <item x="159"/>
-        <item x="33"/>
-        <item x="4"/>
-        <item x="134"/>
-        <item x="60"/>
-        <item x="177"/>
-        <item x="171"/>
-        <item x="185"/>
-        <item x="97"/>
-        <item x="156"/>
-        <item x="12"/>
-        <item x="85"/>
-        <item x="187"/>
-        <item x="69"/>
-        <item x="142"/>
-        <item x="13"/>
-        <item x="149"/>
-        <item x="79"/>
-        <item x="124"/>
-        <item x="5"/>
-        <item x="73"/>
-        <item x="82"/>
-        <item x="103"/>
-        <item x="111"/>
-        <item x="38"/>
-        <item x="18"/>
-        <item x="39"/>
-        <item x="162"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="1"/>
-        <item x="167"/>
-        <item x="117"/>
-        <item x="174"/>
-        <item x="169"/>
-        <item x="24"/>
-        <item x="94"/>
-        <item x="160"/>
-        <item x="178"/>
-        <item x="198"/>
-        <item x="200"/>
-        <item x="41"/>
-        <item x="164"/>
-        <item x="34"/>
-        <item x="120"/>
-        <item x="133"/>
-        <item x="128"/>
-        <item x="173"/>
-        <item x="163"/>
-        <item x="106"/>
-        <item x="138"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="193"/>
-        <item x="147"/>
-        <item x="114"/>
-        <item x="35"/>
-        <item x="116"/>
-        <item x="81"/>
-        <item x="96"/>
-        <item x="166"/>
-        <item x="8"/>
-        <item x="45"/>
-        <item x="126"/>
-        <item x="152"/>
-        <item x="184"/>
-        <item x="98"/>
-        <item x="40"/>
-        <item x="52"/>
-        <item x="3"/>
-        <item x="179"/>
-        <item x="107"/>
-        <item x="71"/>
-        <item x="161"/>
-        <item x="57"/>
-        <item x="76"/>
-        <item x="194"/>
-        <item x="62"/>
-        <item x="26"/>
-        <item x="135"/>
-        <item x="122"/>
-        <item x="83"/>
-        <item x="118"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="50"/>
-        <item x="27"/>
-        <item x="148"/>
-        <item x="44"/>
-        <item x="49"/>
-        <item x="89"/>
-        <item x="189"/>
-        <item x="155"/>
-        <item x="99"/>
-        <item x="2"/>
-        <item x="183"/>
-        <item x="77"/>
-        <item x="140"/>
-        <item x="191"/>
-        <item x="112"/>
-        <item x="28"/>
-        <item x="86"/>
-        <item x="19"/>
-        <item x="110"/>
-        <item x="48"/>
-        <item x="55"/>
-        <item x="88"/>
-        <item x="176"/>
-        <item x="158"/>
-        <item x="72"/>
-        <item x="121"/>
-        <item x="22"/>
-        <item x="132"/>
-        <item x="75"/>
-        <item x="154"/>
-        <item x="109"/>
-        <item x="182"/>
-        <item x="150"/>
-        <item x="36"/>
-        <item x="131"/>
-        <item x="17"/>
-        <item x="137"/>
-        <item x="93"/>
-        <item x="56"/>
-        <item x="16"/>
-        <item x="165"/>
-        <item x="25"/>
-        <item x="192"/>
-        <item x="108"/>
-        <item x="181"/>
-        <item x="91"/>
-        <item x="63"/>
-        <item x="175"/>
-        <item x="136"/>
-        <item x="201"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="9">
+  <rowItems count="10">
     <i>
       <x/>
     </i>
@@ -9966,6 +9463,9 @@
     <i>
       <x v="7"/>
     </i>
+    <i>
+      <x v="8"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -9983,40 +9483,14 @@
   </colItems>
   <dataFields count="2">
     <dataField name="计数项:功能调用类型" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="平均值项:响应时间" fld="3" subtotal="average" baseField="2" baseItem="4"/>
+    <dataField name="平均值项:响应时间" fld="3" subtotal="average" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="9">
-    <format dxfId="10">
+  <formats count="6">
+    <format dxfId="5">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="1">
+          <reference field="2" count="2">
             <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="9">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
             <x v="2"/>
           </reference>
         </references>
@@ -10026,7 +9500,7 @@
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
-            <x v="1"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -10035,13 +9509,13 @@
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
-            <x v="1"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
     </format>
     <format dxfId="2">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+      <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
             <x v="0"/>
@@ -10050,16 +9524,16 @@
       </pivotArea>
     </format>
     <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
-            <x v="0"/>
+            <x v="5"/>
           </reference>
         </references>
       </pivotArea>
     </format>
     <format dxfId="0">
-      <pivotArea dataOnly="0" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
             <x v="5"/>
@@ -10367,13 +9841,13 @@
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="9.75" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="19.75" customWidth="1"/>
     <col min="12" max="12" width="22.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10387,7 +9861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>47</v>
       </c>
@@ -10401,7 +9875,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>92</v>
       </c>
@@ -10415,7 +9889,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>33</v>
       </c>
@@ -10429,7 +9903,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>33</v>
       </c>
@@ -10443,7 +9917,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>48</v>
       </c>
@@ -10457,7 +9931,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>17</v>
       </c>
@@ -10471,7 +9945,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>81</v>
       </c>
@@ -10485,7 +9959,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>18</v>
       </c>
@@ -10499,7 +9973,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>61</v>
       </c>
@@ -10513,7 +9987,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>39</v>
       </c>
@@ -10527,7 +10001,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>35</v>
       </c>
@@ -10541,7 +10015,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>4</v>
       </c>
@@ -10555,7 +10029,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>2</v>
       </c>
@@ -10568,8 +10042,17 @@
       <c r="D14">
         <v>1.77</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="I14" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K14" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>29</v>
       </c>
@@ -10582,8 +10065,17 @@
       <c r="D15">
         <v>1.82</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="I15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="9">
+        <v>111</v>
+      </c>
+      <c r="K15" s="9">
+        <v>2.0499099099099101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>47</v>
       </c>
@@ -10595,6 +10087,15 @@
       </c>
       <c r="D16">
         <v>1.07</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="6">
+        <v>132</v>
+      </c>
+      <c r="K16" s="6">
+        <v>2.0592424242424245</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -10610,6 +10111,15 @@
       <c r="D17">
         <v>1.51</v>
       </c>
+      <c r="I17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="6">
+        <v>133</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1.869022556390977</v>
+      </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
@@ -10624,6 +10134,15 @@
       <c r="D18">
         <v>2.91</v>
       </c>
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="3">
+        <v>125</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1.9974399999999999</v>
+      </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
@@ -10638,6 +10157,15 @@
       <c r="D19">
         <v>2.87</v>
       </c>
+      <c r="I19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="6">
+        <v>137</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1.9803649635036495</v>
+      </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
@@ -10652,6 +10180,15 @@
       <c r="D20">
         <v>1.92</v>
       </c>
+      <c r="I20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="9">
+        <v>119</v>
+      </c>
+      <c r="K20" s="9">
+        <v>2.0738655462184878</v>
+      </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
@@ -10666,6 +10203,15 @@
       <c r="D21">
         <v>2.69</v>
       </c>
+      <c r="I21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="3">
+        <v>120</v>
+      </c>
+      <c r="K21" s="3">
+        <v>2.0355833333333337</v>
+      </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
@@ -10680,6 +10226,15 @@
       <c r="D22">
         <v>1.04</v>
       </c>
+      <c r="I22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="3">
+        <v>123</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1.8879674796747967</v>
+      </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
@@ -10694,6 +10249,11 @@
       <c r="D23">
         <v>1.1399999999999999</v>
       </c>
+      <c r="I23" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
@@ -10708,6 +10268,15 @@
       <c r="D24">
         <v>1.25</v>
       </c>
+      <c r="I24" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1.9922100000000018</v>
+      </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
@@ -10722,15 +10291,6 @@
       <c r="D25">
         <v>2.78</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J25" t="s">
-        <v>1013</v>
-      </c>
-      <c r="K25" t="s">
-        <v>1014</v>
-      </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
@@ -10745,15 +10305,6 @@
       <c r="D26">
         <v>1.42</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="8">
-        <v>111</v>
-      </c>
-      <c r="K26" s="8">
-        <v>2.0499099099099101</v>
-      </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
@@ -10768,15 +10319,6 @@
       <c r="D27">
         <v>2.02</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J27" s="6">
-        <v>132</v>
-      </c>
-      <c r="K27" s="6">
-        <v>2.0592424242424245</v>
-      </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
@@ -10791,15 +10333,6 @@
       <c r="D28">
         <v>2.93</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J28" s="6">
-        <v>133</v>
-      </c>
-      <c r="K28" s="6">
-        <v>1.869022556390977</v>
-      </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
@@ -10814,15 +10347,6 @@
       <c r="D29">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="3">
-        <v>125</v>
-      </c>
-      <c r="K29" s="3">
-        <v>1.9974399999999999</v>
-      </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
@@ -10837,15 +10361,6 @@
       <c r="D30">
         <v>2.5299999999999998</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="6">
-        <v>137</v>
-      </c>
-      <c r="K30" s="6">
-        <v>1.9803649635036495</v>
-      </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
@@ -10860,15 +10375,6 @@
       <c r="D31">
         <v>2.67</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="8">
-        <v>119</v>
-      </c>
-      <c r="K31" s="8">
-        <v>2.0738655462184878</v>
-      </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
@@ -10883,17 +10389,8 @@
       <c r="D32">
         <v>2.36</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="3">
-        <v>120</v>
-      </c>
-      <c r="K32" s="3">
-        <v>2.0355833333333337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>57</v>
       </c>
@@ -10906,17 +10403,8 @@
       <c r="D33">
         <v>2.19</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="3">
-        <v>123</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1.8879674796747967</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>68</v>
       </c>
@@ -10929,17 +10417,8 @@
       <c r="D34">
         <v>1.96</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J34" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K34" s="3">
-        <v>1.9922100000000018</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>33</v>
       </c>
@@ -10953,7 +10432,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>36</v>
       </c>
@@ -10967,7 +10446,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>21</v>
       </c>
@@ -10981,7 +10460,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>47</v>
       </c>
@@ -10995,7 +10474,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>1</v>
       </c>
@@ -11009,7 +10488,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>46</v>
       </c>
@@ -11023,7 +10502,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>2</v>
       </c>
@@ -11037,7 +10516,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>30</v>
       </c>
@@ -11051,7 +10530,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>15</v>
       </c>
@@ -11065,7 +10544,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>17</v>
       </c>
@@ -11079,7 +10558,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>12</v>
       </c>
@@ -11093,7 +10572,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>26</v>
       </c>
@@ -11107,7 +10586,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>100</v>
       </c>
@@ -11121,7 +10600,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>20</v>
       </c>
